--- a/excel/roset-distribuciones-eirl_ruta_proxima_semana.xlsx
+++ b/excel/roset-distribuciones-eirl_ruta_proxima_semana.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rutas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Rutas'!$A$1:$J$577</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Rutas'!$A$1:$J$575</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J577"/>
+  <dimension ref="A1:J575"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -18505,7 +18505,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>C004059847</t>
+          <t>C004059845</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -18515,12 +18515,12 @@
       </c>
       <c r="F348" s="2" t="inlineStr">
         <is>
-          <t>41885644</t>
+          <t>2145929</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>VILCA CHOQUEHUAYTA SARA DIANA</t>
+          <t>COLQUEHUANCA QUISOCALA LAURA</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -18535,7 +18535,7 @@
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>Av. Vidaurrazaga   Mi  Mercado  Puesto 7</t>
+          <t>Av. Vidaurrazaga  Mi Mercado  Puesto  5</t>
         </is>
       </c>
     </row>
@@ -18557,7 +18557,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>C004059845</t>
+          <t>C001458082</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -18567,12 +18567,12 @@
       </c>
       <c r="F349" s="2" t="inlineStr">
         <is>
-          <t>2145929</t>
+          <t>47817278</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>COLQUEHUANCA QUISOCALA LAURA</t>
+          <t>MAYHUA ASENCIO NILDA CRISSTELLIE</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -18587,7 +18587,7 @@
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>Av. Vidaurrazaga  Mi Mercado  Puesto  5</t>
+          <t>AV. AVELINO CACERES URB. MI MERCADO Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
         </is>
       </c>
     </row>
@@ -18609,7 +18609,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>C001428101</t>
+          <t>C001419501</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -18619,12 +18619,12 @@
       </c>
       <c r="F350" s="2" t="inlineStr">
         <is>
-          <t>41988343</t>
+          <t>46884801</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>DIAZ HANCCO BITZAIDA</t>
+          <t>MERMA CAHUANA REYNA</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -18639,7 +18639,7 @@
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>AV. AVELINO CACERES URB. MI MERCADO Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
+          <t>AV. MI MERCADO URB. MI MERCADO Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
         </is>
       </c>
     </row>
@@ -18661,7 +18661,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>C001458082</t>
+          <t>C004161647</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -18671,12 +18671,12 @@
       </c>
       <c r="F351" s="2" t="inlineStr">
         <is>
-          <t>47817278</t>
+          <t>71848585</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>MAYHUA ASENCIO NILDA CRISSTELLIE</t>
+          <t>PINTO TACURI NESTOR ALFREDO</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -18691,7 +18691,7 @@
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>AV. AVELINO CACERES URB. MI MERCADO Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
+          <t>Av. Vidaurrazaga  Mi  Mercado Puesto 19</t>
         </is>
       </c>
     </row>
@@ -18713,22 +18713,22 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>C001419501</t>
+          <t>C001643899</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F352" s="2" t="inlineStr">
         <is>
-          <t>46884801</t>
+          <t>10295721311</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>MERMA CAHUANA REYNA</t>
+          <t>QUEA MENDOZA ENRICA</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -18743,7 +18743,7 @@
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>AV. MI MERCADO URB. MI MERCADO Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
+          <t>AV. VIDAURRAZAGA INT. 26 URB. MI MERCADO Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
         </is>
       </c>
     </row>
@@ -18765,22 +18765,22 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>C004161647</t>
+          <t>C001046956</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F353" s="2" t="inlineStr">
         <is>
-          <t>71848585</t>
+          <t>10295835732</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>PINTO TACURI NESTOR ALFREDO</t>
+          <t>JUSTO LIPA JUANA TERESA</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -18795,7 +18795,7 @@
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>Av. Vidaurrazaga  Mi  Mercado Puesto 19</t>
+          <t>AV. VIDAURRAZAGA PUESTO 28 SE URB. MI MERCADO Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
         </is>
       </c>
     </row>
@@ -18817,22 +18817,22 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>C001643899</t>
+          <t>C004101050</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F354" s="2" t="inlineStr">
         <is>
-          <t>10295721311</t>
+          <t>1783888</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>QUEA MENDOZA ENRICA</t>
+          <t>NINA DE NOLASCO MARTINA</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -18847,7 +18847,7 @@
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>AV. VIDAURRAZAGA INT. 26 URB. MI MERCADO Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
+          <t>av.  vidaurrazaga  mi  mercado  puesto 7</t>
         </is>
       </c>
     </row>
@@ -18869,22 +18869,22 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>C001046956</t>
+          <t>C004203526</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F355" s="2" t="inlineStr">
         <is>
-          <t>10295835732</t>
+          <t>42191041</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>JUSTO LIPA JUANA TERESA</t>
+          <t>HUANCA CAHUAYA MARITZA</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -18894,12 +18894,12 @@
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>José Luis Bustamante Y Rivero (Arequipa)</t>
+          <t>Jacobo Hunter (Arequipa)</t>
         </is>
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>AV. VIDAURRAZAGA PUESTO 28 SE URB. MI MERCADO Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
+          <t>CC Gratersa pasadizo #6,Bloque #1, puesto #2 y 3</t>
         </is>
       </c>
     </row>
@@ -18921,7 +18921,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>C004101050</t>
+          <t>C004210225</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -18931,12 +18931,12 @@
       </c>
       <c r="F356" s="2" t="inlineStr">
         <is>
-          <t>1783888</t>
+          <t>76980005</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>NINA DE NOLASCO MARTINA</t>
+          <t>CONDORI HUANCA YULY PAOLA</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -18946,12 +18946,12 @@
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>José Luis Bustamante Y Rivero (Arequipa)</t>
+          <t>Jacobo Hunter (Arequipa)</t>
         </is>
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>av.  vidaurrazaga  mi  mercado  puesto 7</t>
+          <t>CC. Gratersa  Pasadizo 6 puesto 4 y 5 JLBR</t>
         </is>
       </c>
     </row>
@@ -18973,22 +18973,22 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>C004203526</t>
+          <t>C00C000967</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F357" s="2" t="inlineStr">
         <is>
-          <t>42191041</t>
+          <t>20602385231</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>HUANCA CAHUAYA MARITZA</t>
+          <t>DISTRIBUCIONES PARQQUER SOCIEDAD COMERCI</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -19003,7 +19003,7 @@
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>CC Gratersa pasadizo #6,Bloque #1, puesto #2 y 3</t>
+          <t>V. ANDRES AVELINO CACERES NRO. 101 INT. 13</t>
         </is>
       </c>
     </row>
@@ -19025,7 +19025,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>C004210225</t>
+          <t>C004235658</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -19035,12 +19035,12 @@
       </c>
       <c r="F358" s="2" t="inlineStr">
         <is>
-          <t>76980005</t>
+          <t>1878152</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>CONDORI HUANCA YULY PAOLA</t>
+          <t>CHOQUE CACHICATARI JULIA MARITZA</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -19055,7 +19055,7 @@
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>CC. Gratersa  Pasadizo 6 puesto 4 y 5 JLBR</t>
+          <t>C.C gratersa pasadizo 10 Pto 1 Hunter</t>
         </is>
       </c>
     </row>
@@ -19077,7 +19077,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>C00C000967</t>
+          <t>C001622862</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -19087,12 +19087,12 @@
       </c>
       <c r="F359" s="2" t="inlineStr">
         <is>
-          <t>20602385231</t>
+          <t>20605849203</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>DISTRIBUCIONES PARQQUER SOCIEDAD COMERCI</t>
+          <t>CORPORACION E INVERSIONES BEATRIZ SJT S.</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -19107,14 +19107,14 @@
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>V. ANDRES AVELINO CACERES NRO. 101 INT. 13</t>
+          <t>AV. ANDRES AVELINO CACERES NRO. 101 INT. 2 URB. GRATERSA Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2026-09-16 00:00:00</t>
+          <t>2026-09-17 00:00:00</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -19129,7 +19129,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>C004235658</t>
+          <t>C001694496</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -19139,12 +19139,12 @@
       </c>
       <c r="F360" s="2" t="inlineStr">
         <is>
-          <t>1878152</t>
+          <t>29201738</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>CHOQUE CACHICATARI JULIA MARITZA</t>
+          <t>CANQUI BUSTINZA JULIA</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -19154,19 +19154,19 @@
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>Jacobo Hunter (Arequipa)</t>
+          <t>José Luis Bustamante Y Rivero (Arequipa)</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>C.C gratersa pasadizo 10 Pto 1 Hunter</t>
+          <t>SATELITE CHICO MZA. H LOTE. 1 Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2026-09-16 00:00:00</t>
+          <t>2026-09-17 00:00:00</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -19181,22 +19181,22 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>C001622862</t>
+          <t>C004054228</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F361" s="2" t="inlineStr">
         <is>
-          <t>20605849203</t>
+          <t>47572085</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>CORPORACION E INVERSIONES BEATRIZ SJT S.</t>
+          <t>ESTALLA ESTALLA NELY</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -19206,12 +19206,12 @@
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>Jacobo Hunter (Arequipa)</t>
+          <t>José Luis Bustamante Y Rivero (Arequipa)</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>AV. ANDRES AVELINO CACERES NRO. 101 INT. 2 URB. GRATERSA Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
+          <t>Mariano  Melgar  509  Cerro  Salaverry  JLBYR</t>
         </is>
       </c>
     </row>
@@ -19233,7 +19233,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>C001694496</t>
+          <t>C001428097</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -19243,12 +19243,12 @@
       </c>
       <c r="F362" s="2" t="inlineStr">
         <is>
-          <t>29201738</t>
+          <t>29586309</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>CANQUI BUSTINZA JULIA</t>
+          <t>APAZA SALAS YENY MERCEDES</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -19263,7 +19263,7 @@
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>SATELITE CHICO MZA. H LOTE. 1 Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
+          <t>CL. SANCHEZ TRUJILLO Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
         </is>
       </c>
     </row>
@@ -19285,7 +19285,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>C004054228</t>
+          <t>C001318870</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -19295,12 +19295,12 @@
       </c>
       <c r="F363" s="2" t="inlineStr">
         <is>
-          <t>47572085</t>
+          <t>44143074</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>ESTALLA ESTALLA NELY</t>
+          <t>LAURA ROLDAN LADY DIANA</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -19315,7 +19315,7 @@
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>Mariano  Melgar  509  Cerro  Salaverry  JLBYR</t>
+          <t>BLQ. URB 1RO DE MAYO MZA. B LOTE. 14 URB. CERRO JULY Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
         </is>
       </c>
     </row>
@@ -19337,22 +19337,22 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>C001428097</t>
+          <t>C004100450</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F364" s="2" t="inlineStr">
         <is>
-          <t>29586309</t>
+          <t>10293112911</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>APAZA SALAS YENY MERCEDES</t>
+          <t>MANDAMIENTOS MAMANI IRENE AMPARO</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -19367,7 +19367,7 @@
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>CL. SANCHEZ TRUJILLO Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
+          <t>Calle Sánchez  Trujillo  327  Jose  luis Bustamante y Rivero</t>
         </is>
       </c>
     </row>
@@ -19389,7 +19389,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>C001318870</t>
+          <t>C001716957</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -19399,12 +19399,12 @@
       </c>
       <c r="F365" s="2" t="inlineStr">
         <is>
-          <t>44143074</t>
+          <t>29535598</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>LAURA ROLDAN LADY DIANA</t>
+          <t>GUTIERREZ AVALOS JACQUELINE ESTHER</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -19419,7 +19419,7 @@
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>BLQ. URB 1RO DE MAYO MZA. B LOTE. 14 URB. CERRO JULY Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
+          <t>CL. SANCHEZ TRUJILLO NRO. 400 URB. CERRO SALAVERRY Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
         </is>
       </c>
     </row>
@@ -19441,22 +19441,22 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>C004100450</t>
+          <t>C004054234</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F366" s="2" t="inlineStr">
         <is>
-          <t>10293112911</t>
+          <t>74132643</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>MANDAMIENTOS MAMANI IRENE AMPARO</t>
+          <t>AGUIRRE MACEDO ANGELA CAMILA</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -19471,7 +19471,7 @@
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>Calle Sánchez  Trujillo  327  Jose  luis Bustamante y Rivero</t>
+          <t>Av Sanchez  Trujillo  404  Cerro  Salaverry  Socabaya</t>
         </is>
       </c>
     </row>
@@ -19493,7 +19493,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>C001716957</t>
+          <t>C004201697</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -19503,12 +19503,12 @@
       </c>
       <c r="F367" s="2" t="inlineStr">
         <is>
-          <t>29535598</t>
+          <t>43799325</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>GUTIERREZ AVALOS JACQUELINE ESTHER</t>
+          <t>CHOQUETICO QUISPE WILLIAM</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -19518,12 +19518,12 @@
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>José Luis Bustamante Y Rivero (Arequipa)</t>
+          <t>Jacobo Hunter (Arequipa)</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>CL. SANCHEZ TRUJILLO NRO. 400 URB. CERRO SALAVERRY Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
+          <t>calle Francisco mostajo NRO 358</t>
         </is>
       </c>
     </row>
@@ -19545,7 +19545,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>C004054234</t>
+          <t>C001517514</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -19555,12 +19555,12 @@
       </c>
       <c r="F368" s="2" t="inlineStr">
         <is>
-          <t>74132643</t>
+          <t>22476732</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>AGUIRRE MACEDO ANGELA CAMILA</t>
+          <t>CRISOSTOMO MARTIN TOMAS</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -19575,7 +19575,7 @@
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>Av Sanchez  Trujillo  404  Cerro  Salaverry  Socabaya</t>
+          <t>AV. LAS CONVENCIONES MZA. E LOTE. 6 URB. CERRO JULI Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
         </is>
       </c>
     </row>
@@ -19597,7 +19597,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>C004201697</t>
+          <t>C001666026</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -19607,12 +19607,12 @@
       </c>
       <c r="F369" s="2" t="inlineStr">
         <is>
-          <t>43799325</t>
+          <t>76845213</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>CHOQUETICO QUISPE WILLIAM</t>
+          <t>JUSTO HUERTA JHEYSSY JHENNYFER</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -19622,12 +19622,12 @@
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>Jacobo Hunter (Arequipa)</t>
+          <t>José Luis Bustamante Y Rivero (Arequipa)</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>calle Francisco mostajo NRO 358</t>
+          <t>AV. AVELINO CACERES URB. MI MERCADO PSTO. 27 Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
         </is>
       </c>
     </row>
@@ -19649,7 +19649,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>C001517514</t>
+          <t>C001475575</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -19659,12 +19659,12 @@
       </c>
       <c r="F370" s="2" t="inlineStr">
         <is>
-          <t>22476732</t>
+          <t>30582702</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>CRISOSTOMO MARTIN TOMAS</t>
+          <t>CARPIO ZEGARRA GUILLERMO JUBER</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -19679,7 +19679,7 @@
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>AV. LAS CONVENCIONES MZA. E LOTE. 6 URB. CERRO JULI Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
+          <t>CL. AYARZA NRO. 102 URB. CERRO JULY Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
         </is>
       </c>
     </row>
@@ -19701,7 +19701,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>C001666026</t>
+          <t>C001640895</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -19711,12 +19711,12 @@
       </c>
       <c r="F371" s="2" t="inlineStr">
         <is>
-          <t>76845213</t>
+          <t>29282477</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>JUSTO HUERTA JHEYSSY JHENNYFER</t>
+          <t>MEDINA DE BELLIDO MENEGUNDA LUZ AURORA</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -19726,12 +19726,12 @@
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>José Luis Bustamante Y Rivero (Arequipa)</t>
+          <t>Jacobo Hunter (Arequipa)</t>
         </is>
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>AV. AVELINO CACERES URB. MI MERCADO PSTO. 27 Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
+          <t>CL. AYARZA NRO. 200 URB. CERRO JULY Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
         </is>
       </c>
     </row>
@@ -19753,7 +19753,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>C001475575</t>
+          <t>C004021879</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -19763,12 +19763,12 @@
       </c>
       <c r="F372" s="2" t="inlineStr">
         <is>
-          <t>30582702</t>
+          <t>43241305</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>CARPIO ZEGARRA GUILLERMO JUBER</t>
+          <t>ROJO CACYA ANGELA MARIA</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -19778,12 +19778,12 @@
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>José Luis Bustamante Y Rivero (Arequipa)</t>
+          <t>Jacobo Hunter (Arequipa)</t>
         </is>
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>CL. AYARZA NRO. 102 URB. CERRO JULY Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
+          <t>Calle  Javier  Pérez  de Cuellar D-1</t>
         </is>
       </c>
     </row>
@@ -19805,7 +19805,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>C001640895</t>
+          <t>C004159338</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -19815,12 +19815,12 @@
       </c>
       <c r="F373" s="2" t="inlineStr">
         <is>
-          <t>29282477</t>
+          <t>60783907</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>MEDINA DE BELLIDO MENEGUNDA LUZ AURORA</t>
+          <t>SUPO HUMPIRI DIANA CAROLINA</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -19835,7 +19835,7 @@
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>CL. AYARZA NRO. 200 URB. CERRO JULY Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
+          <t>Terminal La Joya Puesto 4</t>
         </is>
       </c>
     </row>
@@ -19857,7 +19857,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>C004021879</t>
+          <t>C001643880</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -19867,12 +19867,12 @@
       </c>
       <c r="F374" s="2" t="inlineStr">
         <is>
-          <t>43241305</t>
+          <t>47770475</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>ROJO CACYA ANGELA MARIA</t>
+          <t>FUENTES CASTILLA ANA CECILIA</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -19887,7 +19887,7 @@
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>Calle  Javier  Pérez  de Cuellar D-1</t>
+          <t>VILLA HERMOSA MZA. B LOTE. 6 Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
         </is>
       </c>
     </row>
@@ -19909,7 +19909,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>C004159338</t>
+          <t>C001622979</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -19919,12 +19919,12 @@
       </c>
       <c r="F375" s="2" t="inlineStr">
         <is>
-          <t>60783907</t>
+          <t>2439903</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>SUPO HUMPIRI DIANA CAROLINA</t>
+          <t>TURPO MAMANI MOISES EFRAIN</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -19939,7 +19939,7 @@
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>Terminal La Joya Puesto 4</t>
+          <t>URB VILLA HERMOSA MZA. E LOTE. 8 URB. CERRO JULY Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
         </is>
       </c>
     </row>
@@ -19961,7 +19961,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>C001643880</t>
+          <t>C001035344</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -19971,12 +19971,12 @@
       </c>
       <c r="F376" s="2" t="inlineStr">
         <is>
-          <t>47770475</t>
+          <t>29720112</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>FUENTES CASTILLA ANA CECILIA</t>
+          <t>ARHUIRI HUAYLLA JOSE RUFO</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -19991,7 +19991,7 @@
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>VILLA HERMOSA MZA. B LOTE. 6 Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
+          <t>AV. OTR VILLA HERMOZA MD L17 MZA. MAZAA180 LOTE. 17 URB. VILLA HERMOZA Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
         </is>
       </c>
     </row>
@@ -20013,7 +20013,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>C001622979</t>
+          <t>C001640496</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -20023,12 +20023,12 @@
       </c>
       <c r="F377" s="2" t="inlineStr">
         <is>
-          <t>2439903</t>
+          <t>40458328</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>TURPO MAMANI MOISES EFRAIN</t>
+          <t>LOPEZ VASQUEZ LINDA BEILUD</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -20043,7 +20043,7 @@
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>URB VILLA HERMOSA MZA. E LOTE. 8 URB. CERRO JULY Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
+          <t>VILLA HERMOSA MZA. D LOTE. 3 URB. CERRO JULY Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
         </is>
       </c>
     </row>
@@ -20065,22 +20065,22 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>C001035344</t>
+          <t>C001036315</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F378" s="2" t="inlineStr">
         <is>
-          <t>29720112</t>
+          <t>10292542955</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>ARHUIRI HUAYLLA JOSE RUFO</t>
+          <t>MASIAS TORRES ISIDORA</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -20095,7 +20095,7 @@
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>AV. OTR VILLA HERMOZA MD L17 MZA. MAZAA180 LOTE. 17 URB. VILLA HERMOZA Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
+          <t>CERRO JULY MZA. L LOTE. 10 URB. AMP CERRO JULI Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
         </is>
       </c>
     </row>
@@ -20117,7 +20117,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>C001640496</t>
+          <t>C001629121</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -20127,12 +20127,12 @@
       </c>
       <c r="F379" s="2" t="inlineStr">
         <is>
-          <t>40458328</t>
+          <t>29499095</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>LOPEZ VASQUEZ LINDA BEILUD</t>
+          <t>SANCHEZ CONDORI ISABEL GERARDA</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -20147,7 +20147,7 @@
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>VILLA HERMOSA MZA. D LOTE. 3 URB. CERRO JULY Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
+          <t>COOP RIEGO CHILI MZA. H LOTE. 7 Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
         </is>
       </c>
     </row>
@@ -20169,7 +20169,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>C001036315</t>
+          <t>C001038606</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -20179,12 +20179,12 @@
       </c>
       <c r="F380" s="2" t="inlineStr">
         <is>
-          <t>10292542955</t>
+          <t>10247006562</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>MASIAS TORRES ISIDORA</t>
+          <t>ZAPANA VILCA DE APAZA MAXIMILIANA</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -20199,7 +20199,7 @@
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>CERRO JULY MZA. L LOTE. 10 URB. AMP CERRO JULI Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
+          <t>NRO. G INT. 10 URB. COOP DE VIV RIEGO CHILI Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
         </is>
       </c>
     </row>
@@ -20221,22 +20221,22 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>C001629121</t>
+          <t>C004172242</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F381" s="2" t="inlineStr">
         <is>
-          <t>29499095</t>
+          <t>10297032327</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>SANCHEZ CONDORI ISABEL GERARDA</t>
+          <t>PINTO SALAS DE CHAVEZ NELVA MARUJA</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
@@ -20251,7 +20251,7 @@
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>COOP RIEGO CHILI MZA. H LOTE. 7 Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
+          <t>Coop. Rio Chile E - 5 (cerro Juli)</t>
         </is>
       </c>
     </row>
@@ -20273,22 +20273,22 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>C001038606</t>
+          <t>C004043189</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F382" s="2" t="inlineStr">
         <is>
-          <t>10247006562</t>
+          <t>75774443</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>ZAPANA VILCA DE APAZA MAXIMILIANA</t>
+          <t>PARI POLAR DIANA YELEYDA</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -20298,12 +20298,12 @@
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>Jacobo Hunter (Arequipa)</t>
+          <t>José Luis Bustamante Y Rivero (Arequipa)</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>NRO. G INT. 10 URB. COOP DE VIV RIEGO CHILI Arequipa-Arequipa-José Luis Bustamante Y Rivero</t>
+          <t>Urb. Corazón de Jesús Mz. C Lt.9</t>
         </is>
       </c>
     </row>
@@ -20325,22 +20325,22 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>C004172242</t>
+          <t>C001731725</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F383" s="2" t="inlineStr">
         <is>
-          <t>10297032327</t>
+          <t>41127759</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>PINTO SALAS DE CHAVEZ NELVA MARUJA</t>
+          <t>TICONA ARAPA MARISOL MILAGROS</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -20350,19 +20350,19 @@
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>Jacobo Hunter (Arequipa)</t>
+          <t>José Luis Bustamante Y Rivero (Arequipa)</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>Coop. Rio Chile E - 5 (cerro Juli)</t>
+          <t>PJE. HONDURAS PUEBLO JOVEN UNION MZA. M LOTE. 4 URB. COMITE 4 Arequipa-Arequipa-Socabaya</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>2026-09-17 00:00:00</t>
+          <t>2026-09-19 00:00:00</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>C004043189</t>
+          <t>C003001796</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="F384" s="2" t="inlineStr">
         <is>
-          <t>75774443</t>
+          <t>29553934</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>PARI POLAR DIANA YELEYDA</t>
+          <t>GUTIERREZ APAZA ELIZABETH MERCEDES</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -20402,19 +20402,19 @@
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>José Luis Bustamante Y Rivero (Arequipa)</t>
+          <t>Arequipa (Arequipa)</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>Urb. Corazón de Jesús Mz. C Lt.9</t>
+          <t>Urb. Tintaya  Mz. J Lt.13</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2026-09-17 00:00:00</t>
+          <t>2026-09-19 00:00:00</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -20429,7 +20429,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>C001731725</t>
+          <t>C004221541</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -20439,12 +20439,12 @@
       </c>
       <c r="F385" s="2" t="inlineStr">
         <is>
-          <t>41127759</t>
+          <t>73138074</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>TICONA ARAPA MARISOL MILAGROS</t>
+          <t>CRUZ GUTIERREZ ROSSMERY OLENKA</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -20454,12 +20454,12 @@
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>José Luis Bustamante Y Rivero (Arequipa)</t>
+          <t>Arequipa (Arequipa)</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>PJE. HONDURAS PUEBLO JOVEN UNION MZA. M LOTE. 4 URB. COMITE 4 Arequipa-Arequipa-Socabaya</t>
+          <t>Urbanizacion Tintaya Mz J Lot 13 / Jacobo Hunter</t>
         </is>
       </c>
     </row>
@@ -20481,7 +20481,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>C003001796</t>
+          <t>C004170212</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -20491,12 +20491,12 @@
       </c>
       <c r="F386" s="2" t="inlineStr">
         <is>
-          <t>29553934</t>
+          <t>29735260</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>GUTIERREZ APAZA ELIZABETH MERCEDES</t>
+          <t>VILLALOBOS LLOQUE DEYCI RUTH</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -20511,7 +20511,7 @@
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>Urb. Tintaya  Mz. J Lt.13</t>
+          <t>Av Alfonso Ugarte 544</t>
         </is>
       </c>
     </row>
@@ -20533,7 +20533,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>C004221541</t>
+          <t>C003001761</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -20543,12 +20543,12 @@
       </c>
       <c r="F387" s="2" t="inlineStr">
         <is>
-          <t>73138074</t>
+          <t>29639585</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>CRUZ GUTIERREZ ROSSMERY OLENKA</t>
+          <t>CALDERON RAMIREZ ALEX JAVIER</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -20563,7 +20563,7 @@
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>Urbanizacion Tintaya Mz J Lot 13 / Jacobo Hunter</t>
+          <t>calle Bolognesi 502-A tingo</t>
         </is>
       </c>
     </row>
@@ -20585,7 +20585,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>C004170212</t>
+          <t>C001618088</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
@@ -20595,12 +20595,12 @@
       </c>
       <c r="F388" s="2" t="inlineStr">
         <is>
-          <t>29735260</t>
+          <t>45435168</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>VILLALOBOS LLOQUE DEYCI RUTH</t>
+          <t>TURPO MARRON ROXANA</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>Av Alfonso Ugarte 544</t>
+          <t>CL. BOLOGNESI NRO. 414 URB. TINGO Arequipa-Arequipa-Arequipa</t>
         </is>
       </c>
     </row>
@@ -20637,22 +20637,22 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>C003001761</t>
+          <t>C001728169</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F389" s="2" t="inlineStr">
         <is>
-          <t>29639585</t>
+          <t>10417919029</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>CALDERON RAMIREZ ALEX JAVIER</t>
+          <t>RIVERA MUÑOS FIORELLA MARIA</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -20662,12 +20662,12 @@
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>Arequipa (Arequipa)</t>
+          <t>Jacobo Hunter (Arequipa)</t>
         </is>
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>calle Bolognesi 502-A tingo</t>
+          <t>AV. SEPULVEDA NRO. 202 Arequipa-Arequipa-Jacobo Hunter</t>
         </is>
       </c>
     </row>
@@ -20689,22 +20689,22 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>C001618088</t>
+          <t>C001208751</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F390" s="2" t="inlineStr">
         <is>
-          <t>45435168</t>
+          <t>10292773469</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>TURPO MARRON ROXANA</t>
+          <t>PUMA CHOQUE MARIA JOSEFINA</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -20714,12 +20714,12 @@
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>Arequipa (Arequipa)</t>
+          <t>Jacobo Hunter (Arequipa)</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>CL. BOLOGNESI NRO. 414 URB. TINGO Arequipa-Arequipa-Arequipa</t>
+          <t>CL. MORRO DE ARICA NRO. 211 URB. HUNTER Arequipa-Arequipa-Jacobo Hunter</t>
         </is>
       </c>
     </row>
@@ -20741,22 +20741,22 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>C001728169</t>
+          <t>C001454450</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F391" s="2" t="inlineStr">
         <is>
-          <t>10417919029</t>
+          <t>29622195</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>RIVERA MUÑOS FIORELLA MARIA</t>
+          <t>HERNANI RANILLA LOURDES OTILIA</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -20771,7 +20771,7 @@
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>AV. SEPULVEDA NRO. 202 Arequipa-Arequipa-Jacobo Hunter</t>
+          <t>PJE. PSJE LOS ANGELES C-2 VISTA AL MZA. C LOTE. 2 URB. VISTA ALEGRE Arequipa-Arequipa-Jacobo Hunter</t>
         </is>
       </c>
     </row>
@@ -20793,22 +20793,22 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>C001208751</t>
+          <t>C001482988</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F392" s="2" t="inlineStr">
         <is>
-          <t>10292773469</t>
+          <t>29704321</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>PUMA CHOQUE MARIA JOSEFINA</t>
+          <t>CALA HUMPIRI NANCY EUFEMIA</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -20823,7 +20823,7 @@
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>CL. MORRO DE ARICA NRO. 211 URB. HUNTER Arequipa-Arequipa-Jacobo Hunter</t>
+          <t>URB LA COLINA MZA. C LOTE. 4 Arequipa-Arequipa-Jacobo Hunter</t>
         </is>
       </c>
     </row>
@@ -20845,22 +20845,22 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>C001454450</t>
+          <t>C001465940</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F393" s="2" t="inlineStr">
         <is>
-          <t>29622195</t>
+          <t>10297293627</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>HERNANI RANILLA LOURDES OTILIA</t>
+          <t>POMA RODRIGO LAURA</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
@@ -20875,7 +20875,7 @@
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>PJE. PSJE LOS ANGELES C-2 VISTA AL MZA. C LOTE. 2 URB. VISTA ALEGRE Arequipa-Arequipa-Jacobo Hunter</t>
+          <t>URB LA COLINA II MZA. M LOTE. 01 URB. LA COLINA II Arequipa-Arequipa-Jacobo Hunter</t>
         </is>
       </c>
     </row>
@@ -20897,7 +20897,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>C001482988</t>
+          <t>C001576785</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -20907,12 +20907,12 @@
       </c>
       <c r="F394" s="2" t="inlineStr">
         <is>
-          <t>29704321</t>
+          <t>10235689</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>CALA HUMPIRI NANCY EUFEMIA</t>
+          <t>QUISPE QUISPE MARIA CLAUDIA</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -20927,7 +20927,7 @@
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>URB LA COLINA MZA. C LOTE. 4 Arequipa-Arequipa-Jacobo Hunter</t>
+          <t>CL. URB LA COLINA MZA. I LOTE. 3 Arequipa-Arequipa-Jacobo Hunter</t>
         </is>
       </c>
     </row>
@@ -20949,22 +20949,22 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>C001465940</t>
+          <t>C001734874</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F395" s="2" t="inlineStr">
         <is>
-          <t>10297293627</t>
+          <t>41970294</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>POMA RODRIGO LAURA</t>
+          <t>QUENTA CHURA FANNY NORMA</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -20979,7 +20979,7 @@
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>URB LA COLINA II MZA. M LOTE. 01 URB. LA COLINA II Arequipa-Arequipa-Jacobo Hunter</t>
+          <t>AV. AV LAS AMÉRICAS D-3 HUNTER Arequipa-Arequipa-Jacobo Hunter</t>
         </is>
       </c>
     </row>
@@ -21001,7 +21001,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>C001576785</t>
+          <t>C004095833</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -21011,12 +21011,12 @@
       </c>
       <c r="F396" s="2" t="inlineStr">
         <is>
-          <t>10235689</t>
+          <t>40230357</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>QUISPE QUISPE MARIA CLAUDIA</t>
+          <t>CHINO CONDORI YESENIA VERONICA</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -21031,7 +21031,7 @@
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>CL. URB LA COLINA MZA. I LOTE. 3 Arequipa-Arequipa-Jacobo Hunter</t>
+          <t>Av las Américas E-1 Hunter</t>
         </is>
       </c>
     </row>
@@ -21053,22 +21053,22 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>C001734874</t>
+          <t>C003001173</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F397" s="2" t="inlineStr">
         <is>
-          <t>41970294</t>
+          <t>10765575287</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>QUENTA CHURA FANNY NORMA</t>
+          <t>TIPULA GALLEGOS IRMA ISABELA</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -21083,7 +21083,7 @@
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>AV. AV LAS AMÉRICAS D-3 HUNTER Arequipa-Arequipa-Jacobo Hunter</t>
+          <t>pasaje Carlos manchego  131  Hunter</t>
         </is>
       </c>
     </row>
@@ -21105,22 +21105,22 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>C004095833</t>
+          <t>C001202438</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F398" s="2" t="inlineStr">
         <is>
-          <t>40230357</t>
+          <t>10294851076</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>CHINO CONDORI YESENIA VERONICA</t>
+          <t>ROJAS MENDOZA LUCIA</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -21135,7 +21135,7 @@
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>Av las Américas E-1 Hunter</t>
+          <t>CL. BENIGNO BALLON FARFAN NRO. 312 Arequipa-Arequipa-Jacobo Hunter</t>
         </is>
       </c>
     </row>
@@ -21157,22 +21157,22 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>C003001173</t>
+          <t>C004192001</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F399" s="2" t="inlineStr">
         <is>
-          <t>10765575287</t>
+          <t>29596769</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>TIPULA GALLEGOS IRMA ISABELA</t>
+          <t>RAMOS QUISPE RUTH MARY</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
@@ -21187,7 +21187,7 @@
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>pasaje Carlos manchego  131  Hunter</t>
+          <t>calle benigno  Ballón Farfán NRO 319 Hunter</t>
         </is>
       </c>
     </row>
@@ -21209,22 +21209,22 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>C001202438</t>
+          <t>C001706166</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F400" s="2" t="inlineStr">
         <is>
-          <t>10294851076</t>
+          <t>75383408</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>ROJAS MENDOZA LUCIA</t>
+          <t>SILVA FELIPE MARIEL BRIGITTE YOLANDA</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
@@ -21239,7 +21239,7 @@
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>CL. BENIGNO BALLON FARFAN NRO. 312 Arequipa-Arequipa-Jacobo Hunter</t>
+          <t>AV. AV LAS AMERICAS NRO. 102 URB. AV LAS AMERICAS Arequipa-Arequipa-Jacobo Hunter</t>
         </is>
       </c>
     </row>
@@ -21261,7 +21261,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>C004192001</t>
+          <t>C003001510</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -21271,12 +21271,12 @@
       </c>
       <c r="F401" s="2" t="inlineStr">
         <is>
-          <t>29596769</t>
+          <t>30834719</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>RAMOS QUISPE RUTH MARY</t>
+          <t>MOLINA VERA JUAN EDUARDO</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
@@ -21291,7 +21291,7 @@
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>calle benigno  Ballón Farfán NRO 319 Hunter</t>
+          <t>Calle Irlanda D 21 Hunter</t>
         </is>
       </c>
     </row>
@@ -21313,7 +21313,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>C001706166</t>
+          <t>C001201967</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
@@ -21323,12 +21323,12 @@
       </c>
       <c r="F402" s="2" t="inlineStr">
         <is>
-          <t>75383408</t>
+          <t>29555412</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>SILVA FELIPE MARIEL BRIGITTE YOLANDA</t>
+          <t>MANCHEGO DE ANDIA FILOMENA LUZ</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
@@ -21343,7 +21343,7 @@
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>AV. AV LAS AMERICAS NRO. 102 URB. AV LAS AMERICAS Arequipa-Arequipa-Jacobo Hunter</t>
+          <t>CL. IRLANDA NRO. 103 Arequipa-Arequipa-Jacobo Hunter</t>
         </is>
       </c>
     </row>
@@ -21365,7 +21365,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>C003001510</t>
+          <t>C001211394</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
@@ -21375,12 +21375,12 @@
       </c>
       <c r="F403" s="2" t="inlineStr">
         <is>
-          <t>30834719</t>
+          <t>29469219</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>MOLINA VERA JUAN EDUARDO</t>
+          <t>GARCIA ALFARO ROSARIO AMELIA</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
@@ -21395,7 +21395,7 @@
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>Calle Irlanda D 21 Hunter</t>
+          <t>AV. AVE ITALIA NRO. 110 URB. HUNTER Arequipa-Arequipa-Jacobo Hunter</t>
         </is>
       </c>
     </row>
@@ -21417,7 +21417,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>C001201967</t>
+          <t>C001333266</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -21427,12 +21427,12 @@
       </c>
       <c r="F404" s="2" t="inlineStr">
         <is>
-          <t>29555412</t>
+          <t>74203330</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>MANCHEGO DE ANDIA FILOMENA LUZ</t>
+          <t>VALDIVIA MACHACA JESSICA MARIELENA</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -21447,7 +21447,7 @@
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>CL. IRLANDA NRO. 103 Arequipa-Arequipa-Jacobo Hunter</t>
+          <t>MCDO. VICTORIA CORSO ZEGARRA PSTO. 03 Arequipa-Arequipa-Jacobo Hunter</t>
         </is>
       </c>
     </row>
@@ -21469,7 +21469,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>C001211394</t>
+          <t>C004094864</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -21479,12 +21479,12 @@
       </c>
       <c r="F405" s="2" t="inlineStr">
         <is>
-          <t>29469219</t>
+          <t>71502450</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>GARCIA ALFARO ROSARIO AMELIA</t>
+          <t>COLLAO MACHADO MILITZA THAMARA</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
@@ -21499,7 +21499,7 @@
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>AV. AVE ITALIA NRO. 110 URB. HUNTER Arequipa-Arequipa-Jacobo Hunter</t>
+          <t>Av  Italia  207 -A Jacobo Hunter</t>
         </is>
       </c>
     </row>
@@ -21521,7 +21521,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>C001333266</t>
+          <t>C001457850</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -21531,12 +21531,12 @@
       </c>
       <c r="F406" s="2" t="inlineStr">
         <is>
-          <t>74203330</t>
+          <t>29596553</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>VALDIVIA MACHACA JESSICA MARIELENA</t>
+          <t>ZEVALLOS FUENTES YOLANDA</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -21551,7 +21551,7 @@
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>MCDO. VICTORIA CORSO ZEGARRA PSTO. 03 Arequipa-Arequipa-Jacobo Hunter</t>
+          <t>AV. PAISAJISTA MZA. E LOTE. 2 URB. 28 DE JULIO Arequipa-Arequipa-Jacobo Hunter</t>
         </is>
       </c>
     </row>
@@ -21573,22 +21573,22 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>C004094864</t>
+          <t>C001205412</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F407" s="2" t="inlineStr">
         <is>
-          <t>71502450</t>
+          <t>10294807999</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>COLLAO MACHADO MILITZA THAMARA</t>
+          <t>COILA CAPACOILA MARIA</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
@@ -21603,14 +21603,14 @@
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>Av  Italia  207 -A Jacobo Hunter</t>
+          <t>AV. PAISAJISTA MZA. C LOTE. 18 Arequipa-Arequipa-Jacobo Hunter</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>2026-09-19 00:00:00</t>
+          <t>2026-09-18 00:00:00</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -21625,7 +21625,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>C001457850</t>
+          <t>C003001798</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -21635,12 +21635,12 @@
       </c>
       <c r="F408" s="2" t="inlineStr">
         <is>
-          <t>29596553</t>
+          <t>29555926</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>ZEVALLOS FUENTES YOLANDA</t>
+          <t>ANCO YANA NELLY LINA</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -21655,14 +21655,14 @@
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>AV. PAISAJISTA MZA. E LOTE. 2 URB. 28 DE JULIO Arequipa-Arequipa-Jacobo Hunter</t>
+          <t>Calle  Paraguay 106 Hunter</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>2026-09-19 00:00:00</t>
+          <t>2026-09-18 00:00:00</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -21677,22 +21677,22 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>C001205412</t>
+          <t>C001478825</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F409" s="2" t="inlineStr">
         <is>
-          <t>10294807999</t>
+          <t>29623493</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>COILA CAPACOILA MARIA</t>
+          <t>HUILLCA GARCIA BEATRIZ</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -21707,7 +21707,7 @@
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>AV. PAISAJISTA MZA. C LOTE. 18 Arequipa-Arequipa-Jacobo Hunter</t>
+          <t>AV. SAN MARTIN DE PORRES MZA. I LOTE. 3 URB. SAN MARTIN DE PORRES Arequipa-Arequipa-Jacobo Hunter</t>
         </is>
       </c>
     </row>
@@ -21729,7 +21729,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>C003001798</t>
+          <t>C001579646</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
@@ -21739,12 +21739,12 @@
       </c>
       <c r="F410" s="2" t="inlineStr">
         <is>
-          <t>29555926</t>
+          <t>42650255</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>ANCO YANA NELLY LINA</t>
+          <t>MAMANI VILCA JESSIKA MERCEDES</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -21759,7 +21759,7 @@
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>Calle  Paraguay 106 Hunter</t>
+          <t>CL. LAS PEÑAS PASAJE CALVARIO NRO. 101 URB. JACOBO HUNTER Arequipa-Arequipa-Jacobo Hunter</t>
         </is>
       </c>
     </row>
@@ -21781,7 +21781,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>C001478825</t>
+          <t>C004001782</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -21791,12 +21791,12 @@
       </c>
       <c r="F411" s="2" t="inlineStr">
         <is>
-          <t>29623493</t>
+          <t>29556006</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>HUILLCA GARCIA BEATRIZ</t>
+          <t>ARIAS RAMOS EULALIA</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
@@ -21811,7 +21811,7 @@
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>AV. SAN MARTIN DE PORRES MZA. I LOTE. 3 URB. SAN MARTIN DE PORRES Arequipa-Arequipa-Jacobo Hunter</t>
+          <t>Buenos Aires  615</t>
         </is>
       </c>
     </row>
@@ -21833,7 +21833,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>C001579646</t>
+          <t>C003001617</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -21843,12 +21843,12 @@
       </c>
       <c r="F412" s="2" t="inlineStr">
         <is>
-          <t>42650255</t>
+          <t>80212995</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>MAMANI VILCA JESSIKA MERCEDES</t>
+          <t>ALVAREZ VILLAROEL DAMIANA NELLY</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -21863,7 +21863,7 @@
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>CL. LAS PEÑAS PASAJE CALVARIO NRO. 101 URB. JACOBO HUNTER Arequipa-Arequipa-Jacobo Hunter</t>
+          <t>Calle Bella Arequipa 102 psje. Micaela  Bastidas Hunter</t>
         </is>
       </c>
     </row>
@@ -21885,22 +21885,22 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>C004001782</t>
+          <t>C001200852</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F413" s="2" t="inlineStr">
         <is>
-          <t>29556006</t>
+          <t>10296251211</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>ARIAS RAMOS EULALIA</t>
+          <t>CUNO ROJAS PATRICIA</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
@@ -21915,7 +21915,7 @@
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>Buenos Aires  615</t>
+          <t>PJE. MICAELA BASTIDAS NRO. A INT. 1 URB. AA HH LOS ANGELES Arequipa-Arequipa-Jacobo Hunter</t>
         </is>
       </c>
     </row>
@@ -21937,7 +21937,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>C003001617</t>
+          <t>C003001432</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -21947,12 +21947,12 @@
       </c>
       <c r="F414" s="2" t="inlineStr">
         <is>
-          <t>80212995</t>
+          <t>41844507</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>ALVAREZ VILLAROEL DAMIANA NELLY</t>
+          <t>MAMANI ENCINAS LAURA YANETH</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -21967,7 +21967,7 @@
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>Calle Bella Arequipa 102 psje. Micaela  Bastidas Hunter</t>
+          <t>Calle Belén Nro 106 San Juan de Dios - Jacobo hunter</t>
         </is>
       </c>
     </row>
@@ -21989,22 +21989,22 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>C001200852</t>
+          <t>C004215975</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F415" s="2" t="inlineStr">
         <is>
-          <t>10296251211</t>
+          <t>41235725</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>CUNO ROJAS PATRICIA</t>
+          <t>MAYTA DIAZ EDWIN</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
@@ -22019,7 +22019,7 @@
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>PJE. MICAELA BASTIDAS NRO. A INT. 1 URB. AA HH LOS ANGELES Arequipa-Arequipa-Jacobo Hunter</t>
+          <t>calle belen no 106 san juan de Dios</t>
         </is>
       </c>
     </row>
@@ -22041,7 +22041,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>C003001432</t>
+          <t>C004101186</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -22051,12 +22051,12 @@
       </c>
       <c r="F416" s="2" t="inlineStr">
         <is>
-          <t>41844507</t>
+          <t>73874370</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>MAMANI ENCINAS LAURA YANETH</t>
+          <t>CACYA PACO JACKELYN</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -22071,7 +22071,7 @@
       </c>
       <c r="J416" t="inlineStr">
         <is>
-          <t>Calle Belén Nro 106 San Juan de Dios - Jacobo hunter</t>
+          <t>Av. Tahuantinsuyo   LL 1 ampliación  pampas  del  cuzco  Hunter</t>
         </is>
       </c>
     </row>
@@ -22093,7 +22093,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>C004215975</t>
+          <t>C001734913</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -22103,12 +22103,12 @@
       </c>
       <c r="F417" s="2" t="inlineStr">
         <is>
-          <t>41235725</t>
+          <t>48133640</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>MAYTA DIAZ EDWIN</t>
+          <t>HERRERA COAQUIRA ROSSY</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -22123,7 +22123,7 @@
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>calle belen no 106 san juan de Dios</t>
+          <t>AV. AVENIDA TAHUANTISUYO H 2 HUNTE Arequipa-Arequipa-Jacobo Hunter</t>
         </is>
       </c>
     </row>
@@ -22145,7 +22145,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>C004101186</t>
+          <t>C004174415</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
@@ -22155,12 +22155,12 @@
       </c>
       <c r="F418" s="2" t="inlineStr">
         <is>
-          <t>73874370</t>
+          <t>29644772</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>CACYA PACO JACKELYN</t>
+          <t>QUISPE CAYTE ELOY CESAR</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
@@ -22175,7 +22175,7 @@
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>Av. Tahuantinsuyo   LL 1 ampliación  pampas  del  cuzco  Hunter</t>
+          <t>Av Tahuantinsuyo frente a la posta R - 3</t>
         </is>
       </c>
     </row>
@@ -22197,7 +22197,7 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>C001734913</t>
+          <t>C001734885</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
@@ -22207,12 +22207,12 @@
       </c>
       <c r="F419" s="2" t="inlineStr">
         <is>
-          <t>48133640</t>
+          <t>29644752</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>HERRERA COAQUIRA ROSSY</t>
+          <t>CONDORI RODRIGUEZ CARLITA LEONOR</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
@@ -22227,7 +22227,7 @@
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>AV. AVENIDA TAHUANTISUYO H 2 HUNTE Arequipa-Arequipa-Jacobo Hunter</t>
+          <t>AV. AV TAHUANTINSUYO B-1 AMPLIACI Arequipa-Arequipa-Jacobo Hunter</t>
         </is>
       </c>
     </row>
@@ -22249,7 +22249,7 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>C004174415</t>
+          <t>C001526442</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -22259,12 +22259,12 @@
       </c>
       <c r="F420" s="2" t="inlineStr">
         <is>
-          <t>29644772</t>
+          <t>43460722</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>QUISPE CAYTE ELOY CESAR</t>
+          <t>RAMOS ALVAREZ VILMA</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
@@ -22279,7 +22279,7 @@
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>Av Tahuantinsuyo frente a la posta R - 3</t>
+          <t>AV. TUPAC AMARU MZA. LL LOTE. 11 URB. HUNTER Arequipa-Arequipa-Jacobo Hunter</t>
         </is>
       </c>
     </row>
@@ -22301,7 +22301,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>C001734885</t>
+          <t>C003001579</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -22311,12 +22311,12 @@
       </c>
       <c r="F421" s="2" t="inlineStr">
         <is>
-          <t>29644752</t>
+          <t>43730765</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>CONDORI RODRIGUEZ CARLITA LEONOR</t>
+          <t>CCOSI PHOCCO DAVID LIZANDRO</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
@@ -22331,7 +22331,7 @@
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>AV. AV TAHUANTINSUYO B-1 AMPLIACI Arequipa-Arequipa-Jacobo Hunter</t>
+          <t>Calle Huáscar Mz E Lt 4 A</t>
         </is>
       </c>
     </row>
@@ -22353,7 +22353,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>C001526442</t>
+          <t>C001708514</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
@@ -22363,12 +22363,12 @@
       </c>
       <c r="F422" s="2" t="inlineStr">
         <is>
-          <t>43460722</t>
+          <t>29581110</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>RAMOS ALVAREZ VILMA</t>
+          <t>YDME QUISPE SUSANA</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
@@ -22383,7 +22383,7 @@
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>AV. TUPAC AMARU MZA. LL LOTE. 11 URB. HUNTER Arequipa-Arequipa-Jacobo Hunter</t>
+          <t>CL. CALLE ATAHUALPA MZA. Q LOTE. 6 URB. AMPLIACIÓN PAMAPAS DEL CUZCO Arequipa-Arequipa-Jacobo Hunter</t>
         </is>
       </c>
     </row>
@@ -22405,22 +22405,22 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>C003001579</t>
+          <t>C001213825</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F423" s="2" t="inlineStr">
         <is>
-          <t>43730765</t>
+          <t>10296685092</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>CCOSI PHOCCO DAVID LIZANDRO</t>
+          <t>DIAZ CUEVASO JUSTA</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
@@ -22435,7 +22435,7 @@
       </c>
       <c r="J423" t="inlineStr">
         <is>
-          <t>Calle Huáscar Mz E Lt 4 A</t>
+          <t>AV. FRANSISCO BOLOGNESI MZA. P LOTE. 3 URB. 13 DE AGOSTO Arequipa-Arequipa-Jacobo Hunter</t>
         </is>
       </c>
     </row>
@@ -22457,7 +22457,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>C001708514</t>
+          <t>C003001548</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
@@ -22467,12 +22467,12 @@
       </c>
       <c r="F424" s="2" t="inlineStr">
         <is>
-          <t>29581110</t>
+          <t>29614603</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>YDME QUISPE SUSANA</t>
+          <t>HUALLA BEJAR VICTORIA</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
@@ -22487,7 +22487,7 @@
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>CL. CALLE ATAHUALPA MZA. Q LOTE. 6 URB. AMPLIACIÓN PAMAPAS DEL CUZCO Arequipa-Arequipa-Jacobo Hunter</t>
+          <t>Av fco Bolognesi  mz A lt 2 -  13 de agosto</t>
         </is>
       </c>
     </row>
@@ -22509,7 +22509,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>C001213825</t>
+          <t>C001224485</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
@@ -22519,12 +22519,12 @@
       </c>
       <c r="F425" s="2" t="inlineStr">
         <is>
-          <t>10296685092</t>
+          <t>10296732287</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>DIAZ CUEVASO JUSTA</t>
+          <t>APAZA MAMANI JONILY SILVIA</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
@@ -22539,7 +22539,7 @@
       </c>
       <c r="J425" t="inlineStr">
         <is>
-          <t>AV. FRANSISCO BOLOGNESI MZA. P LOTE. 3 URB. 13 DE AGOSTO Arequipa-Arequipa-Jacobo Hunter</t>
+          <t>CL. SANCHEZ CERRO MZA. E LOTE. 21 Arequipa-Arequipa-Jacobo Hunter</t>
         </is>
       </c>
     </row>
@@ -22561,7 +22561,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>C003001548</t>
+          <t>C001381351</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -22571,12 +22571,12 @@
       </c>
       <c r="F426" s="2" t="inlineStr">
         <is>
-          <t>29614603</t>
+          <t>29643763</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>HUALLA BEJAR VICTORIA</t>
+          <t>LOPEZ TURPO CESAR</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
@@ -22591,7 +22591,7 @@
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>Av fco Bolognesi  mz A lt 2 -  13 de agosto</t>
+          <t>AV. SAN MIGUEL DE PIURA NRO. 415 Arequipa-Arequipa-Jacobo Hunter</t>
         </is>
       </c>
     </row>
@@ -22613,22 +22613,22 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>C001224485</t>
+          <t>C004096815</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F427" s="2" t="inlineStr">
         <is>
-          <t>10296732287</t>
+          <t>46018643</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>APAZA MAMANI JONILY SILVIA</t>
+          <t>HUANCA ROJAS ROSALIA PORFIRIA</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
@@ -22643,7 +22643,7 @@
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>CL. SANCHEZ CERRO MZA. E LOTE. 21 Arequipa-Arequipa-Jacobo Hunter</t>
+          <t>calle Ollantay mz O  lote 7   Ampliación  pampas del cuzco  Hunter</t>
         </is>
       </c>
     </row>
@@ -22665,7 +22665,7 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>C001381351</t>
+          <t>C001208746</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
@@ -22675,12 +22675,12 @@
       </c>
       <c r="F428" s="2" t="inlineStr">
         <is>
-          <t>29643763</t>
+          <t>29731940</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>LOPEZ TURPO CESAR</t>
+          <t>CASTILLO TORRES SALOME</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
@@ -22695,7 +22695,7 @@
       </c>
       <c r="J428" t="inlineStr">
         <is>
-          <t>AV. SAN MIGUEL DE PIURA NRO. 415 Arequipa-Arequipa-Jacobo Hunter</t>
+          <t>AV. TAHUANTINSUYO MZA. M LOTE. 26 Arequipa-Arequipa-Jacobo Hunter</t>
         </is>
       </c>
     </row>
@@ -22717,7 +22717,7 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>C004096815</t>
+          <t>C004214923</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
@@ -22727,12 +22727,12 @@
       </c>
       <c r="F429" s="2" t="inlineStr">
         <is>
-          <t>46018643</t>
+          <t>29582660</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>HUANCA ROJAS ROSALIA PORFIRIA</t>
+          <t>CHOQUETICO GUTIERREZ YRMA SALOME</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
@@ -22747,7 +22747,7 @@
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>calle Ollantay mz O  lote 7   Ampliación  pampas del cuzco  Hunter</t>
+          <t>Av tahuantinsuyo Mf lt 9</t>
         </is>
       </c>
     </row>
@@ -22769,22 +22769,22 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>C001208746</t>
+          <t>C001201889</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F430" s="2" t="inlineStr">
         <is>
-          <t>29731940</t>
+          <t>10294744423</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>CASTILLO TORRES SALOME</t>
+          <t>MEZA GOMEZ MARGOT</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
@@ -22799,7 +22799,7 @@
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>AV. TAHUANTINSUYO MZA. M LOTE. 26 Arequipa-Arequipa-Jacobo Hunter</t>
+          <t>CL. DIAGONAL URB. URB PAMPA DEL CUZCO Arequipa-Arequipa-Jacobo Hunter</t>
         </is>
       </c>
     </row>
@@ -22821,7 +22821,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>C004214923</t>
+          <t>C001688431</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
@@ -22831,12 +22831,12 @@
       </c>
       <c r="F431" s="2" t="inlineStr">
         <is>
-          <t>29582660</t>
+          <t>46370872</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>CHOQUETICO GUTIERREZ YRMA SALOME</t>
+          <t>CONDORI QUISPE VICTORIA</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
@@ -22851,19 +22851,19 @@
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>Av tahuantinsuyo Mf lt 9</t>
+          <t>Garcilazo de la Vega lote 1 MZA  E Hunter</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>2026-09-18 00:00:00</t>
+          <t>2026-09-14 00:00:00</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
+          <t>RONALD LLULIAN SANDOVAL GANOZA</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -22873,22 +22873,22 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>C001201889</t>
+          <t>C003001795</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F432" s="2" t="inlineStr">
         <is>
-          <t>10294744423</t>
+          <t>23846072</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>MEZA GOMEZ MARGOT</t>
+          <t>OVALLE RODRIGUEZ TERESA</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
@@ -22898,24 +22898,24 @@
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>Jacobo Hunter (Arequipa)</t>
+          <t>Socabaya (Arequipa)</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>CL. DIAGONAL URB. URB PAMPA DEL CUZCO Arequipa-Arequipa-Jacobo Hunter</t>
+          <t>UPIS  Paisajista Y-7 Hunter</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>2026-09-18 00:00:00</t>
+          <t>2026-09-14 00:00:00</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
+          <t>RONALD LLULIAN SANDOVAL GANOZA</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -22925,7 +22925,7 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>C001688431</t>
+          <t>C004045354</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
@@ -22935,12 +22935,12 @@
       </c>
       <c r="F433" s="2" t="inlineStr">
         <is>
-          <t>46370872</t>
+          <t>29643876</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>CONDORI QUISPE VICTORIA</t>
+          <t>COTACALLAPA URVIOLA VILMA VERONICA</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -22950,12 +22950,12 @@
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>Jacobo Hunter (Arequipa)</t>
+          <t>Socabaya (Arequipa)</t>
         </is>
       </c>
       <c r="J433" t="inlineStr">
         <is>
-          <t>Garcilazo de la Vega lote 1 MZA  E Hunter</t>
+          <t>UPIS  Paisajista  T'-1 Hunter.</t>
         </is>
       </c>
     </row>
@@ -22977,7 +22977,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>C003001795</t>
+          <t>C004162486</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -22987,12 +22987,12 @@
       </c>
       <c r="F434" s="2" t="inlineStr">
         <is>
-          <t>23846072</t>
+          <t>29474642</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>OVALLE RODRIGUEZ TERESA</t>
+          <t>COILA PANCA FRANCISCO ROGELIO</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
@@ -23007,7 +23007,7 @@
       </c>
       <c r="J434" t="inlineStr">
         <is>
-          <t>UPIS  Paisajista Y-7 Hunter</t>
+          <t>Asociación Upis Paisajista Mz T- lot 1</t>
         </is>
       </c>
     </row>
@@ -23029,7 +23029,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>C004045354</t>
+          <t>C004210131</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
@@ -23039,12 +23039,12 @@
       </c>
       <c r="F435" s="2" t="inlineStr">
         <is>
-          <t>29643876</t>
+          <t>47075454</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>COTACALLAPA URVIOLA VILMA VERONICA</t>
+          <t>CORRALES MUÑOZ ELIZABETH DELIA</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -23059,7 +23059,7 @@
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>UPIS  Paisajista  T'-1 Hunter.</t>
+          <t>Upis paisajista Mz L lote 1 Hunter</t>
         </is>
       </c>
     </row>
@@ -23081,7 +23081,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>C004162486</t>
+          <t>C004222670</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
@@ -23091,12 +23091,12 @@
       </c>
       <c r="F436" s="2" t="inlineStr">
         <is>
-          <t>29474642</t>
+          <t>41278691</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>COILA PANCA FRANCISCO ROGELIO</t>
+          <t>DUEÑAS CHICASACA SOLEDAD ANA</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
@@ -23111,7 +23111,7 @@
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>Asociación Upis Paisajista Mz T- lot 1</t>
+          <t>La mansion1 D-17 SOCABAYA</t>
         </is>
       </c>
     </row>
@@ -23133,7 +23133,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>C004210131</t>
+          <t>C004222572</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
@@ -23143,12 +23143,12 @@
       </c>
       <c r="F437" s="2" t="inlineStr">
         <is>
-          <t>47075454</t>
+          <t>80198384</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>CORRALES MUÑOZ ELIZABETH DELIA</t>
+          <t>FLOREZ CONDORI BRAULIA</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -23163,7 +23163,7 @@
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>Upis paisajista Mz L lote 1 Hunter</t>
+          <t>URB La mansion 1 Mz LL Lote 16 Socabaya</t>
         </is>
       </c>
     </row>
@@ -23185,7 +23185,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>C004222670</t>
+          <t>C004222527</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
@@ -23195,12 +23195,12 @@
       </c>
       <c r="F438" s="2" t="inlineStr">
         <is>
-          <t>41278691</t>
+          <t>44884143</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>DUEÑAS CHICASACA SOLEDAD ANA</t>
+          <t>PUMA AQUINO GUIDO</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
@@ -23215,7 +23215,7 @@
       </c>
       <c r="J438" t="inlineStr">
         <is>
-          <t>La mansion1 D-17 SOCABAYA</t>
+          <t>URB La mansion 1 Mz M lote 9 Socabaya</t>
         </is>
       </c>
     </row>
@@ -23237,7 +23237,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>C004222572</t>
+          <t>C004222538</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
@@ -23247,12 +23247,12 @@
       </c>
       <c r="F439" s="2" t="inlineStr">
         <is>
-          <t>80198384</t>
+          <t>25010352</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>FLOREZ CONDORI BRAULIA</t>
+          <t>QUISPE HUAYHUA JULIA ROSA</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -23267,7 +23267,7 @@
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>URB La mansion 1 Mz LL Lote 16 Socabaya</t>
+          <t>La Mansión II De Socabaya Mza-D Lte-5</t>
         </is>
       </c>
     </row>
@@ -23289,7 +23289,7 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>C004222527</t>
+          <t>C004222549</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
@@ -23299,12 +23299,12 @@
       </c>
       <c r="F440" s="2" t="inlineStr">
         <is>
-          <t>44884143</t>
+          <t>40863070</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>PUMA AQUINO GUIDO</t>
+          <t>MAMANI VILCA ELSA</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -23319,7 +23319,7 @@
       </c>
       <c r="J440" t="inlineStr">
         <is>
-          <t>URB La mansion 1 Mz M lote 9 Socabaya</t>
+          <t>La Mansión II De Socabaya Mza-M Lte-23</t>
         </is>
       </c>
     </row>
@@ -23341,7 +23341,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>C004222538</t>
+          <t>C004222616</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
@@ -23351,12 +23351,12 @@
       </c>
       <c r="F441" s="2" t="inlineStr">
         <is>
-          <t>25010352</t>
+          <t>47353661</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>QUISPE HUAYHUA JULIA ROSA</t>
+          <t>SIVINCHA HUAYHUA ALEX ABEL</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
@@ -23371,7 +23371,7 @@
       </c>
       <c r="J441" t="inlineStr">
         <is>
-          <t>La Mansión II De Socabaya Mza-D Lte-5</t>
+          <t>La Mansión II De Socabaya Mza-I Lte-9</t>
         </is>
       </c>
     </row>
@@ -23393,7 +23393,7 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>C004222549</t>
+          <t>C004222612</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
@@ -23403,12 +23403,12 @@
       </c>
       <c r="F442" s="2" t="inlineStr">
         <is>
-          <t>40863070</t>
+          <t>41037383</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>MAMANI VILCA ELSA</t>
+          <t>MIRANDA LINARES MARITZA</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
@@ -23423,7 +23423,7 @@
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>La Mansión II De Socabaya Mza-M Lte-23</t>
+          <t>La Mansión II De Socabaya Mza-C Lte-21</t>
         </is>
       </c>
     </row>
@@ -23445,7 +23445,7 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>C004222616</t>
+          <t>C004222621</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
@@ -23455,12 +23455,12 @@
       </c>
       <c r="F443" s="2" t="inlineStr">
         <is>
-          <t>47353661</t>
+          <t>60469755</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>SIVINCHA HUAYHUA ALEX ABEL</t>
+          <t>LLOSA MAMANI CAMILO SANTOS</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
@@ -23475,7 +23475,7 @@
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>La Mansión II De Socabaya Mza-I Lte-9</t>
+          <t>La Mansión II De Socabaya Mza-G Lte-1</t>
         </is>
       </c>
     </row>
@@ -23497,7 +23497,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>C004222612</t>
+          <t>C001327072</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
@@ -23507,12 +23507,12 @@
       </c>
       <c r="F444" s="2" t="inlineStr">
         <is>
-          <t>41037383</t>
+          <t>29683039</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>MIRANDA LINARES MARITZA</t>
+          <t>QUISPE PANIBRA MARTINA</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
@@ -23522,12 +23522,12 @@
       </c>
       <c r="I444" t="inlineStr">
         <is>
-          <t>Socabaya (Arequipa)</t>
+          <t>Sachaca (Arequipa)</t>
         </is>
       </c>
       <c r="J444" t="inlineStr">
         <is>
-          <t>La Mansión II De Socabaya Mza-C Lte-21</t>
+          <t>ASOC ALATA MZA. B LOTE. 12 Arequipa-Arequipa-Sachaca</t>
         </is>
       </c>
     </row>
@@ -23549,7 +23549,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>C004222621</t>
+          <t>C001556812</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
@@ -23559,12 +23559,12 @@
       </c>
       <c r="F445" s="2" t="inlineStr">
         <is>
-          <t>60469755</t>
+          <t>29510876</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>LLOSA MAMANI CAMILO SANTOS</t>
+          <t>CHACON CHURA JUSTINA</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
@@ -23574,12 +23574,12 @@
       </c>
       <c r="I445" t="inlineStr">
         <is>
-          <t>Socabaya (Arequipa)</t>
+          <t>Sachaca (Arequipa)</t>
         </is>
       </c>
       <c r="J445" t="inlineStr">
         <is>
-          <t>La Mansión II De Socabaya Mza-G Lte-1</t>
+          <t>JC MARIATEGUI NRO. 150 URB. ALATA SACHACA Arequipa-Arequipa-Sachaca</t>
         </is>
       </c>
     </row>
@@ -23601,7 +23601,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>C001327072</t>
+          <t>C001471615</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
@@ -23611,12 +23611,12 @@
       </c>
       <c r="F446" s="2" t="inlineStr">
         <is>
-          <t>29683039</t>
+          <t>45956934</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>QUISPE PANIBRA MARTINA</t>
+          <t>CONDORI HUANCA DENCI MEDALID</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
@@ -23631,7 +23631,7 @@
       </c>
       <c r="J446" t="inlineStr">
         <is>
-          <t>ASOC ALATA MZA. B LOTE. 12 Arequipa-Arequipa-Sachaca</t>
+          <t>CL. MARCARANI MZA. C LOTE. 2 URB. SACHACA Arequipa-Arequipa-Sachaca</t>
         </is>
       </c>
     </row>
@@ -23653,7 +23653,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>C001556812</t>
+          <t>C004199833</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
@@ -23663,12 +23663,12 @@
       </c>
       <c r="F447" s="2" t="inlineStr">
         <is>
-          <t>29510876</t>
+          <t>80448473</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>CHACON CHURA JUSTINA</t>
+          <t>CAHUI MAMANI EVA MILAGROS</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
@@ -23678,12 +23678,12 @@
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t>Sachaca (Arequipa)</t>
+          <t>Tiabaya (Arequipa)</t>
         </is>
       </c>
       <c r="J447" t="inlineStr">
         <is>
-          <t>JC MARIATEGUI NRO. 150 URB. ALATA SACHACA Arequipa-Arequipa-Sachaca</t>
+          <t>Pueblo Joven 7 de junio mz N lote 6</t>
         </is>
       </c>
     </row>
@@ -23705,7 +23705,7 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>C001471615</t>
+          <t>C001493203</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
@@ -23715,12 +23715,12 @@
       </c>
       <c r="F448" s="2" t="inlineStr">
         <is>
-          <t>45956934</t>
+          <t>29651986</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>CONDORI HUANCA DENCI MEDALID</t>
+          <t>APAZA MERMA ALFONSA BARIA</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
@@ -23730,12 +23730,12 @@
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>Sachaca (Arequipa)</t>
+          <t>Tiabaya (Arequipa)</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
         <is>
-          <t>CL. MARCARANI MZA. C LOTE. 2 URB. SACHACA Arequipa-Arequipa-Sachaca</t>
+          <t>PJ 7 DE JUNIO MZA. D LOTE. 1 URB. PJ 7 DE JUNIO SACHACA Arequipa-Arequipa-Sachaca</t>
         </is>
       </c>
     </row>
@@ -23757,7 +23757,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>C004199833</t>
+          <t>C001510861</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
@@ -23767,12 +23767,12 @@
       </c>
       <c r="F449" s="2" t="inlineStr">
         <is>
-          <t>80448473</t>
+          <t>29645482</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>CAHUI MAMANI EVA MILAGROS</t>
+          <t>HUAMANI ROQUE FELIPE</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
@@ -23787,7 +23787,7 @@
       </c>
       <c r="J449" t="inlineStr">
         <is>
-          <t>Pueblo Joven 7 de junio mz N lote 6</t>
+          <t>PPJJ 7 DE JUNIO MZA. C LOTE. 10 URB. 7 DE JUNIO SACHACA Arequipa-Arequipa-Sachaca</t>
         </is>
       </c>
     </row>
@@ -23809,22 +23809,22 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>C001493203</t>
+          <t>C001615865</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F450" s="2" t="inlineStr">
         <is>
-          <t>29651986</t>
+          <t>10294793939</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>APAZA MERMA ALFONSA BARIA</t>
+          <t>ZEGARRA ARIAS LUZ ELENA</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
@@ -23834,12 +23834,12 @@
       </c>
       <c r="I450" t="inlineStr">
         <is>
-          <t>Tiabaya (Arequipa)</t>
+          <t>Sachaca (Arequipa)</t>
         </is>
       </c>
       <c r="J450" t="inlineStr">
         <is>
-          <t>PJ 7 DE JUNIO MZA. D LOTE. 1 URB. PJ 7 DE JUNIO SACHACA Arequipa-Arequipa-Sachaca</t>
+          <t>AV. ARANCOTA NRO. 124 URB. SACHACA Arequipa-Arequipa-Sachaca</t>
         </is>
       </c>
     </row>
@@ -23861,7 +23861,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>C001510861</t>
+          <t>C001732556</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
@@ -23871,12 +23871,12 @@
       </c>
       <c r="F451" s="2" t="inlineStr">
         <is>
-          <t>29645482</t>
+          <t>71923959</t>
         </is>
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>HUAMANI ROQUE FELIPE</t>
+          <t>DIAZ CHIRINOS PEDRO PAOLO</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
@@ -23886,12 +23886,12 @@
       </c>
       <c r="I451" t="inlineStr">
         <is>
-          <t>Tiabaya (Arequipa)</t>
+          <t>Sachaca (Arequipa)</t>
         </is>
       </c>
       <c r="J451" t="inlineStr">
         <is>
-          <t>PPJJ 7 DE JUNIO MZA. C LOTE. 10 URB. 7 DE JUNIO SACHACA Arequipa-Arequipa-Sachaca</t>
+          <t>AV. AV ARANCOTA 111 SACHACA NRO. 111 Arequipa-Arequipa-Sachaca</t>
         </is>
       </c>
     </row>
@@ -23913,22 +23913,22 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>C001615865</t>
+          <t>C004101986</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F452" s="2" t="inlineStr">
         <is>
-          <t>10294793939</t>
+          <t>74236257</t>
         </is>
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>ZEGARRA ARIAS LUZ ELENA</t>
+          <t>GAMARRA DELGADO JOSE ARMANDO</t>
         </is>
       </c>
       <c r="H452" t="inlineStr">
@@ -23943,7 +23943,7 @@
       </c>
       <c r="J452" t="inlineStr">
         <is>
-          <t>AV. ARANCOTA NRO. 124 URB. SACHACA Arequipa-Arequipa-Sachaca</t>
+          <t>Av. Arancota 102 Sachaca</t>
         </is>
       </c>
     </row>
@@ -23965,7 +23965,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>C001732556</t>
+          <t>C001729179</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
@@ -23975,12 +23975,12 @@
       </c>
       <c r="F453" s="2" t="inlineStr">
         <is>
-          <t>71923959</t>
+          <t>29309110</t>
         </is>
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>DIAZ CHIRINOS PEDRO PAOLO</t>
+          <t>MANRIQUE RIVAS ELIZABETH LILI</t>
         </is>
       </c>
       <c r="H453" t="inlineStr">
@@ -23995,7 +23995,7 @@
       </c>
       <c r="J453" t="inlineStr">
         <is>
-          <t>AV. AV ARANCOTA 111 SACHACA NRO. 111 Arequipa-Arequipa-Sachaca</t>
+          <t>AV. ARANCOTA 107 SACHACA NRO. 107 Arequipa-Arequipa-Sachaca</t>
         </is>
       </c>
     </row>
@@ -24017,7 +24017,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>C004101986</t>
+          <t>C001204435</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
@@ -24027,12 +24027,12 @@
       </c>
       <c r="F454" s="2" t="inlineStr">
         <is>
-          <t>74236257</t>
+          <t>29476607</t>
         </is>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>GAMARRA DELGADO JOSE ARMANDO</t>
+          <t>TITI DE MACHACA HONORATA</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
@@ -24047,7 +24047,7 @@
       </c>
       <c r="J454" t="inlineStr">
         <is>
-          <t>Av. Arancota 102 Sachaca</t>
+          <t>LA PARADA TINGO PSTO. 47 Arequipa-Arequipa-Sachaca</t>
         </is>
       </c>
     </row>
@@ -24069,7 +24069,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>C001729179</t>
+          <t>C004204999</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
@@ -24079,12 +24079,12 @@
       </c>
       <c r="F455" s="2" t="inlineStr">
         <is>
-          <t>29309110</t>
+          <t>74301555</t>
         </is>
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>MANRIQUE RIVAS ELIZABETH LILI</t>
+          <t>MARQUEZ HUAICCANE EDINSON FLAVIO</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
@@ -24099,14 +24099,14 @@
       </c>
       <c r="J455" t="inlineStr">
         <is>
-          <t>AV. ARANCOTA 107 SACHACA NRO. 107 Arequipa-Arequipa-Sachaca</t>
+          <t>La Parada de Tingo puesto 48,  Sachaca</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>2026-09-14 00:00:00</t>
+          <t>2026-09-15 00:00:00</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -24121,22 +24121,22 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>C001204435</t>
+          <t>C001549070</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F456" s="2" t="inlineStr">
         <is>
-          <t>29476607</t>
+          <t>10293502884</t>
         </is>
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>TITI DE MACHACA HONORATA</t>
+          <t>INFANTAS PORTILLA YORI ISABEL</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
@@ -24151,14 +24151,14 @@
       </c>
       <c r="J456" t="inlineStr">
         <is>
-          <t>LA PARADA TINGO PSTO. 47 Arequipa-Arequipa-Sachaca</t>
+          <t>NRO. G INT. 23 URB. EL PALACIO ETAPA II Arequipa-Arequipa-Sachaca</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>2026-09-14 00:00:00</t>
+          <t>2026-09-15 00:00:00</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -24173,22 +24173,22 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>C004204999</t>
+          <t>C001725963</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F457" s="2" t="inlineStr">
         <is>
-          <t>74301555</t>
+          <t>10251203275</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>MARQUEZ HUAICCANE EDINSON FLAVIO</t>
+          <t>FLORES DE GARRIDO NATIVIDAD</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
@@ -24203,7 +24203,7 @@
       </c>
       <c r="J457" t="inlineStr">
         <is>
-          <t>La Parada de Tingo puesto 48,  Sachaca</t>
+          <t>MZA. G LOTE. 18 URB. URB EL PALACIO Arequipa-Arequipa-Sachaca</t>
         </is>
       </c>
     </row>
@@ -24225,7 +24225,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>C001549070</t>
+          <t>C001207910</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
@@ -24235,12 +24235,12 @@
       </c>
       <c r="F458" s="2" t="inlineStr">
         <is>
-          <t>10293502884</t>
+          <t>10295161529</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>INFANTAS PORTILLA YORI ISABEL</t>
+          <t>ZENTENO TALAVERA NORA MARITZA</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
@@ -24255,7 +24255,7 @@
       </c>
       <c r="J458" t="inlineStr">
         <is>
-          <t>NRO. G INT. 23 URB. EL PALACIO ETAPA II Arequipa-Arequipa-Sachaca</t>
+          <t>MZA. M LOTE. 4 URB. EL PALACIO II Arequipa-Arequipa-Sachaca</t>
         </is>
       </c>
     </row>
@@ -24277,22 +24277,22 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>C001725963</t>
+          <t>C001480950</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F459" s="2" t="inlineStr">
         <is>
-          <t>10251203275</t>
+          <t>44931585</t>
         </is>
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>FLORES DE GARRIDO NATIVIDAD</t>
+          <t>DURAN CRUZ TANIA</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
@@ -24307,7 +24307,7 @@
       </c>
       <c r="J459" t="inlineStr">
         <is>
-          <t>MZA. G LOTE. 18 URB. URB EL PALACIO Arequipa-Arequipa-Sachaca</t>
+          <t>CL. LOS JASMINEZ MZA. O LOTE. 20 URB. CAMPO VERDE Arequipa-Arequipa-Sachaca</t>
         </is>
       </c>
     </row>
@@ -24329,7 +24329,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>C001207910</t>
+          <t>C001201127</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
@@ -24339,12 +24339,12 @@
       </c>
       <c r="F460" s="2" t="inlineStr">
         <is>
-          <t>10295161529</t>
+          <t>10296707525</t>
         </is>
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>ZENTENO TALAVERA NORA MARITZA</t>
+          <t>MONTOYA GARCIA LUZ MARINA</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
@@ -24359,7 +24359,7 @@
       </c>
       <c r="J460" t="inlineStr">
         <is>
-          <t>MZA. M LOTE. 4 URB. EL PALACIO II Arequipa-Arequipa-Sachaca</t>
+          <t>JR. CAL VALENCIA FRANCISCO N103 NRO. 103 MZA. MAZAA320 Arequipa-Arequipa-Sachaca</t>
         </is>
       </c>
     </row>
@@ -24381,7 +24381,7 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>C001480950</t>
+          <t>C001668702</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
@@ -24391,12 +24391,12 @@
       </c>
       <c r="F461" s="2" t="inlineStr">
         <is>
-          <t>44931585</t>
+          <t>40809135</t>
         </is>
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>DURAN CRUZ TANIA</t>
+          <t>AGUIRRE TAPIA RUTH LUZ MARINA</t>
         </is>
       </c>
       <c r="H461" t="inlineStr">
@@ -24411,7 +24411,7 @@
       </c>
       <c r="J461" t="inlineStr">
         <is>
-          <t>CL. LOS JASMINEZ MZA. O LOTE. 20 URB. CAMPO VERDE Arequipa-Arequipa-Sachaca</t>
+          <t>CL. TAMAYO NRO. 3 URB. PT SACHACA Arequipa-Arequipa-Sachaca</t>
         </is>
       </c>
     </row>
@@ -24433,22 +24433,22 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>C001201127</t>
+          <t>C001572067</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F462" s="2" t="inlineStr">
         <is>
-          <t>10296707525</t>
+          <t>46706185</t>
         </is>
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>MONTOYA GARCIA LUZ MARINA</t>
+          <t>ROSADO FRISANCHO MILAGROS ESTELA</t>
         </is>
       </c>
       <c r="H462" t="inlineStr">
@@ -24463,7 +24463,7 @@
       </c>
       <c r="J462" t="inlineStr">
         <is>
-          <t>JR. CAL VALENCIA FRANCISCO N103 NRO. 103 MZA. MAZAA320 Arequipa-Arequipa-Sachaca</t>
+          <t>CL. CALLE TAMAYO NRO. 103 Arequipa-Arequipa-Sachaca</t>
         </is>
       </c>
     </row>
@@ -24485,7 +24485,7 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>C001668702</t>
+          <t>C001211854</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
@@ -24495,12 +24495,12 @@
       </c>
       <c r="F463" s="2" t="inlineStr">
         <is>
-          <t>40809135</t>
+          <t>29478044</t>
         </is>
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>AGUIRRE TAPIA RUTH LUZ MARINA</t>
+          <t>MANRIQUE SALAS DIANA LIBERTAD</t>
         </is>
       </c>
       <c r="H463" t="inlineStr">
@@ -24515,7 +24515,7 @@
       </c>
       <c r="J463" t="inlineStr">
         <is>
-          <t>CL. TAMAYO NRO. 3 URB. PT SACHACA Arequipa-Arequipa-Sachaca</t>
+          <t>CL. MIGUEL GRAU NRO. 119 URB. SACHACA Arequipa-Arequipa-Sachaca</t>
         </is>
       </c>
     </row>
@@ -24537,7 +24537,7 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>C001572067</t>
+          <t>C003001615</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
@@ -24547,12 +24547,12 @@
       </c>
       <c r="F464" s="2" t="inlineStr">
         <is>
-          <t>46706185</t>
+          <t>29708137</t>
         </is>
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>ROSADO FRISANCHO MILAGROS ESTELA</t>
+          <t>SOTELO MANRIQUE JEANETH MELINA</t>
         </is>
       </c>
       <c r="H464" t="inlineStr">
@@ -24567,7 +24567,7 @@
       </c>
       <c r="J464" t="inlineStr">
         <is>
-          <t>CL. CALLE TAMAYO NRO. 103 Arequipa-Arequipa-Sachaca</t>
+          <t>Calle Bolognesi número 101</t>
         </is>
       </c>
     </row>
@@ -24589,7 +24589,7 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>C001211854</t>
+          <t>C001714220</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
@@ -24599,12 +24599,12 @@
       </c>
       <c r="F465" s="2" t="inlineStr">
         <is>
-          <t>29478044</t>
+          <t>29476398</t>
         </is>
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>MANRIQUE SALAS DIANA LIBERTAD</t>
+          <t>VELAZCO LINARES ALBERTO LUIS</t>
         </is>
       </c>
       <c r="H465" t="inlineStr">
@@ -24619,7 +24619,7 @@
       </c>
       <c r="J465" t="inlineStr">
         <is>
-          <t>CL. MIGUEL GRAU NRO. 119 URB. SACHACA Arequipa-Arequipa-Sachaca</t>
+          <t>CL. 2 DE MAYO NRO. 108 Arequipa-Arequipa-Sachaca</t>
         </is>
       </c>
     </row>
@@ -24641,7 +24641,7 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>C003001615</t>
+          <t>C003007102</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
@@ -24651,12 +24651,12 @@
       </c>
       <c r="F466" s="2" t="inlineStr">
         <is>
-          <t>29708137</t>
+          <t>30843790</t>
         </is>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>SOTELO MANRIQUE JEANETH MELINA</t>
+          <t>DIAZ DAVILA MILAGRITOS MARIA</t>
         </is>
       </c>
       <c r="H466" t="inlineStr">
@@ -24671,7 +24671,7 @@
       </c>
       <c r="J466" t="inlineStr">
         <is>
-          <t>Calle Bolognesi número 101</t>
+          <t>urb el palacio I mz j lote 6 int c</t>
         </is>
       </c>
     </row>
@@ -24693,22 +24693,22 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>C001714220</t>
+          <t>C001209616</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F467" s="2" t="inlineStr">
         <is>
-          <t>29476398</t>
+          <t>10294776856</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>VELAZCO LINARES ALBERTO LUIS</t>
+          <t>RODRIGUEZ DE PAREDES NORMA SABINA</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">
@@ -24723,7 +24723,7 @@
       </c>
       <c r="J467" t="inlineStr">
         <is>
-          <t>CL. 2 DE MAYO NRO. 108 Arequipa-Arequipa-Sachaca</t>
+          <t>CL. INDEPENDENCIA NRO. 138 URB. SACHACA Arequipa-Arequipa-Sachaca</t>
         </is>
       </c>
     </row>
@@ -24745,7 +24745,7 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>C003007102</t>
+          <t>C004201005</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
@@ -24755,12 +24755,12 @@
       </c>
       <c r="F468" s="2" t="inlineStr">
         <is>
-          <t>30843790</t>
+          <t>4644006</t>
         </is>
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>DIAZ DAVILA MILAGRITOS MARIA</t>
+          <t>HUANCA BRAVO ROSA ELENA</t>
         </is>
       </c>
       <c r="H468" t="inlineStr">
@@ -24775,7 +24775,7 @@
       </c>
       <c r="J468" t="inlineStr">
         <is>
-          <t>urb el palacio I mz j lote 6 int c</t>
+          <t>av fernandini 104</t>
         </is>
       </c>
     </row>
@@ -24797,22 +24797,22 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>C001209616</t>
+          <t>C00C001024</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F469" s="2" t="inlineStr">
         <is>
-          <t>10294776856</t>
+          <t>44245966</t>
         </is>
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>RODRIGUEZ DE PAREDES NORMA SABINA</t>
+          <t>ALCAZAR CALDERON CARMEN HILDA</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
@@ -24827,7 +24827,7 @@
       </c>
       <c r="J469" t="inlineStr">
         <is>
-          <t>CL. INDEPENDENCIA NRO. 138 URB. SACHACA Arequipa-Arequipa-Sachaca</t>
+          <t>Cerro la Aparecida MzA lt3</t>
         </is>
       </c>
     </row>
@@ -24849,7 +24849,7 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>C004201005</t>
+          <t>C004174763</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
@@ -24859,12 +24859,12 @@
       </c>
       <c r="F470" s="2" t="inlineStr">
         <is>
-          <t>4644006</t>
+          <t>29721840</t>
         </is>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>HUANCA BRAVO ROSA ELENA</t>
+          <t>GUTIERREZ RAMOS FELICITAS</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
@@ -24879,7 +24879,7 @@
       </c>
       <c r="J470" t="inlineStr">
         <is>
-          <t>av fernandini 104</t>
+          <t>Urb.el Dorado Mz.K.lote 9</t>
         </is>
       </c>
     </row>
@@ -24901,22 +24901,22 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>C00C001024</t>
+          <t>C001213984</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F471" s="2" t="inlineStr">
         <is>
-          <t>44245966</t>
+          <t>10294228620</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>ALCAZAR CALDERON CARMEN HILDA</t>
+          <t>FLORES FERNANDEZ ANA MARIA</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
@@ -24931,7 +24931,7 @@
       </c>
       <c r="J471" t="inlineStr">
         <is>
-          <t>Cerro la Aparecida MzA lt3</t>
+          <t>MZA. R LOTE. 16 URB. EL DORADO Arequipa-Arequipa-Sachaca</t>
         </is>
       </c>
     </row>
@@ -24953,22 +24953,22 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>C004174763</t>
+          <t>C004167713</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F472" s="2" t="inlineStr">
         <is>
-          <t>29721840</t>
+          <t>10308266830</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>GUTIERREZ RAMOS FELICITAS</t>
+          <t>TERNERO GAMBOA ISOLINA JANET</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
@@ -24983,7 +24983,7 @@
       </c>
       <c r="J472" t="inlineStr">
         <is>
-          <t>Urb.el Dorado Mz.K.lote 9</t>
+          <t>Residencial el Ensueño 1 Mz.C.Lote 1</t>
         </is>
       </c>
     </row>
@@ -25005,7 +25005,7 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>C001213984</t>
+          <t>C004213934</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
@@ -25015,12 +25015,12 @@
       </c>
       <c r="F473" s="2" t="inlineStr">
         <is>
-          <t>10294228620</t>
+          <t>10443523192</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>FLORES FERNANDEZ ANA MARIA</t>
+          <t>ANAYA HUAYHUA DE ESPINOZA MIRIAM GLORIA</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
@@ -25035,7 +25035,7 @@
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>MZA. R LOTE. 16 URB. EL DORADO Arequipa-Arequipa-Sachaca</t>
+          <t>Pasos del senor sin número sachaca Referencia frente al colegio invoca schooll</t>
         </is>
       </c>
     </row>
@@ -25057,22 +25057,22 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>C004167713</t>
+          <t>C001537943</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F474" s="2" t="inlineStr">
         <is>
-          <t>10308266830</t>
+          <t>44470142</t>
         </is>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>TERNERO GAMBOA ISOLINA JANET</t>
+          <t>NINA CALCINA RUTH MARIBEL</t>
         </is>
       </c>
       <c r="H474" t="inlineStr">
@@ -25082,12 +25082,12 @@
       </c>
       <c r="I474" t="inlineStr">
         <is>
-          <t>Sachaca (Arequipa)</t>
+          <t>Tiabaya (Arequipa)</t>
         </is>
       </c>
       <c r="J474" t="inlineStr">
         <is>
-          <t>Residencial el Ensueño 1 Mz.C.Lote 1</t>
+          <t>CORAZON DE JESUS MZA. I LOTE. 7 URB. CORAZON DE JESUS SACHACA Arequipa-Arequipa-Sachaca</t>
         </is>
       </c>
     </row>
@@ -25109,7 +25109,7 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>C004213934</t>
+          <t>C001491486</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
@@ -25119,12 +25119,12 @@
       </c>
       <c r="F475" s="2" t="inlineStr">
         <is>
-          <t>10443523192</t>
+          <t>10308627433</t>
         </is>
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>ANAYA HUAYHUA DE ESPINOZA MIRIAM GLORIA</t>
+          <t>QUISPE CUSI MELITON</t>
         </is>
       </c>
       <c r="H475" t="inlineStr">
@@ -25134,12 +25134,12 @@
       </c>
       <c r="I475" t="inlineStr">
         <is>
-          <t>Sachaca (Arequipa)</t>
+          <t>Tiabaya (Arequipa)</t>
         </is>
       </c>
       <c r="J475" t="inlineStr">
         <is>
-          <t>Pasos del senor sin número sachaca Referencia frente al colegio invoca schooll</t>
+          <t>COM1 MZA. K LOTE. 5 URB. PEDRO VILCAPAZA-COMITE 1 Arequipa-Arequipa-Sachaca</t>
         </is>
       </c>
     </row>
@@ -25161,7 +25161,7 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>C001537943</t>
+          <t>C004207318</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
@@ -25171,12 +25171,12 @@
       </c>
       <c r="F476" s="2" t="inlineStr">
         <is>
-          <t>44470142</t>
+          <t>46781612</t>
         </is>
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>NINA CALCINA RUTH MARIBEL</t>
+          <t>PALLE CONDORI URSULA JOSEFINA</t>
         </is>
       </c>
       <c r="H476" t="inlineStr">
@@ -25191,7 +25191,7 @@
       </c>
       <c r="J476" t="inlineStr">
         <is>
-          <t>CORAZON DE JESUS MZA. I LOTE. 7 URB. CORAZON DE JESUS SACHACA Arequipa-Arequipa-Sachaca</t>
+          <t>Pueblo jovenPedro vilcapaza mz t Lote 1, Sachaca</t>
         </is>
       </c>
     </row>
@@ -25213,22 +25213,22 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>C001491486</t>
+          <t>C001474485</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F477" s="2" t="inlineStr">
         <is>
-          <t>10308627433</t>
+          <t>41493277</t>
         </is>
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>QUISPE CUSI MELITON</t>
+          <t>ANAYA HUAYHUA OLIVIA VERONICA</t>
         </is>
       </c>
       <c r="H477" t="inlineStr">
@@ -25243,7 +25243,7 @@
       </c>
       <c r="J477" t="inlineStr">
         <is>
-          <t>COM1 MZA. K LOTE. 5 URB. PEDRO VILCAPAZA-COMITE 1 Arequipa-Arequipa-Sachaca</t>
+          <t>AV. PASOS DEL SEÑOR NRO. 141 URB. AAHH CHIRIHUANA - SACHACA Arequipa-Arequipa-Sachaca</t>
         </is>
       </c>
     </row>
@@ -25265,7 +25265,7 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>C004207318</t>
+          <t>C001199758</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
@@ -25275,12 +25275,12 @@
       </c>
       <c r="F478" s="2" t="inlineStr">
         <is>
-          <t>46781612</t>
+          <t>29646042</t>
         </is>
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>PALLE CONDORI URSULA JOSEFINA</t>
+          <t>MACHACA MAITA ROSA CONSUELO</t>
         </is>
       </c>
       <c r="H478" t="inlineStr">
@@ -25295,7 +25295,7 @@
       </c>
       <c r="J478" t="inlineStr">
         <is>
-          <t>Pueblo jovenPedro vilcapaza mz t Lote 1, Sachaca</t>
+          <t>CL. PASOS DEL SEÑOR NRO. 129 URB. PASOS DEL SEÑOR Arequipa-Arequipa-Sachaca</t>
         </is>
       </c>
     </row>
@@ -25317,7 +25317,7 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>C001474485</t>
+          <t>C001669432</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
@@ -25327,12 +25327,12 @@
       </c>
       <c r="F479" s="2" t="inlineStr">
         <is>
-          <t>41493277</t>
+          <t>29550622</t>
         </is>
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>ANAYA HUAYHUA OLIVIA VERONICA</t>
+          <t>QUISPE CONDORI DE CALCINA VICENTA AQUELI</t>
         </is>
       </c>
       <c r="H479" t="inlineStr">
@@ -25347,14 +25347,14 @@
       </c>
       <c r="J479" t="inlineStr">
         <is>
-          <t>AV. PASOS DEL SEÑOR NRO. 141 URB. AAHH CHIRIHUANA - SACHACA Arequipa-Arequipa-Sachaca</t>
+          <t>VICTOR MALDONADO MZA. E LOTE. 4 URB. PASOS DEL SEÑOR Arequipa-Arequipa-Sachaca</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>2026-09-15 00:00:00</t>
+          <t>2026-09-16 00:00:00</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -25369,7 +25369,7 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>C001199758</t>
+          <t>C001670952</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="F480" s="2" t="inlineStr">
         <is>
-          <t>29646042</t>
+          <t>42211721</t>
         </is>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>MACHACA MAITA ROSA CONSUELO</t>
+          <t>FALCON NINARAQUI IRENI JANETH</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
@@ -25399,14 +25399,14 @@
       </c>
       <c r="J480" t="inlineStr">
         <is>
-          <t>CL. PASOS DEL SEÑOR NRO. 129 URB. PASOS DEL SEÑOR Arequipa-Arequipa-Sachaca</t>
+          <t>PPJJ 7 DE JUNIO ZONA A MZA. C LOTE. 10 Arequipa-Arequipa-Sachaca</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>2026-09-15 00:00:00</t>
+          <t>2026-09-16 00:00:00</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -25421,7 +25421,7 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>C001669432</t>
+          <t>C004048995</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
@@ -25431,12 +25431,12 @@
       </c>
       <c r="F481" s="2" t="inlineStr">
         <is>
-          <t>29550622</t>
+          <t>45771823</t>
         </is>
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>QUISPE CONDORI DE CALCINA VICENTA AQUELI</t>
+          <t>ROJAS QUISPE SAYDA MARISA</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
@@ -25451,7 +25451,7 @@
       </c>
       <c r="J481" t="inlineStr">
         <is>
-          <t>VICTOR MALDONADO MZA. E LOTE. 4 URB. PASOS DEL SEÑOR Arequipa-Arequipa-Sachaca</t>
+          <t>Asoc. Tupac  Amaru  Mz.C  Lote 3 Sachaca</t>
         </is>
       </c>
     </row>
@@ -25473,7 +25473,7 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>C001670952</t>
+          <t>C001730223</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
@@ -25483,12 +25483,12 @@
       </c>
       <c r="F482" s="2" t="inlineStr">
         <is>
-          <t>42211721</t>
+          <t>73965165</t>
         </is>
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>FALCON NINARAQUI IRENI JANETH</t>
+          <t>CCACCALA YAMPASI EMILIA</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
@@ -25503,7 +25503,7 @@
       </c>
       <c r="J482" t="inlineStr">
         <is>
-          <t>PPJJ 7 DE JUNIO ZONA A MZA. C LOTE. 10 Arequipa-Arequipa-Sachaca</t>
+          <t>AV. AS PEDRO VILCAPAZA MZ N LOT 6 LOTE. 6 Arequipa-Arequipa-Sachaca</t>
         </is>
       </c>
     </row>
@@ -25525,7 +25525,7 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>C004048995</t>
+          <t>C001211826</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
@@ -25535,12 +25535,12 @@
       </c>
       <c r="F483" s="2" t="inlineStr">
         <is>
-          <t>45771823</t>
+          <t>28974053</t>
         </is>
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>ROJAS QUISPE SAYDA MARISA</t>
+          <t>PALACIOS ACAPANA LUPE EULALIA</t>
         </is>
       </c>
       <c r="H483" t="inlineStr">
@@ -25555,7 +25555,7 @@
       </c>
       <c r="J483" t="inlineStr">
         <is>
-          <t>Asoc. Tupac  Amaru  Mz.C  Lote 3 Sachaca</t>
+          <t>PP JJ 8 DE DICIEMBRE MZA. P LOTE. 4 URB. PJ 8 DE DICIEMBRE Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -25577,7 +25577,7 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>C001730223</t>
+          <t>C004093581</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
@@ -25587,12 +25587,12 @@
       </c>
       <c r="F484" s="2" t="inlineStr">
         <is>
-          <t>73965165</t>
+          <t>76414831</t>
         </is>
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>CCACCALA YAMPASI EMILIA</t>
+          <t>CHANINE FLORES LUZ MARINA</t>
         </is>
       </c>
       <c r="H484" t="inlineStr">
@@ -25607,7 +25607,7 @@
       </c>
       <c r="J484" t="inlineStr">
         <is>
-          <t>AV. AS PEDRO VILCAPAZA MZ N LOT 6 LOTE. 6 Arequipa-Arequipa-Sachaca</t>
+          <t>8  de  diciembre  mz b Lote 5 tiabaya</t>
         </is>
       </c>
     </row>
@@ -25629,7 +25629,7 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>C001211826</t>
+          <t>C001656404</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
@@ -25639,12 +25639,12 @@
       </c>
       <c r="F485" s="2" t="inlineStr">
         <is>
-          <t>28974053</t>
+          <t>29683002</t>
         </is>
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>PALACIOS ACAPANA LUPE EULALIA</t>
+          <t>GALDOS BENAVENTE LUZ EUSEBIA</t>
         </is>
       </c>
       <c r="H485" t="inlineStr">
@@ -25659,7 +25659,7 @@
       </c>
       <c r="J485" t="inlineStr">
         <is>
-          <t>PP JJ 8 DE DICIEMBRE MZA. P LOTE. 4 URB. PJ 8 DE DICIEMBRE Arequipa-Arequipa-Tiabaya</t>
+          <t>8 DE DICIEMBRE ZONA A COMITE MZA. C LOTE. 9 Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -25681,7 +25681,7 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>C004093581</t>
+          <t>C001329398</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
@@ -25691,12 +25691,12 @@
       </c>
       <c r="F486" s="2" t="inlineStr">
         <is>
-          <t>76414831</t>
+          <t>29508944</t>
         </is>
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>CHANINE FLORES LUZ MARINA</t>
+          <t>DE LA CRUZ MAMANI GREGORIO</t>
         </is>
       </c>
       <c r="H486" t="inlineStr">
@@ -25711,7 +25711,7 @@
       </c>
       <c r="J486" t="inlineStr">
         <is>
-          <t>8  de  diciembre  mz b Lote 5 tiabaya</t>
+          <t>PJ 8 DE DICIEMBRE MZA. C LOTE. 11 URB. PJ 8 DE DICIEMBRE Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -25733,7 +25733,7 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>C001656404</t>
+          <t>C001523060</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
@@ -25743,12 +25743,12 @@
       </c>
       <c r="F487" s="2" t="inlineStr">
         <is>
-          <t>29683002</t>
+          <t>43353413</t>
         </is>
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>GALDOS BENAVENTE LUZ EUSEBIA</t>
+          <t>TTURO QUISPE ROXANA LIZI</t>
         </is>
       </c>
       <c r="H487" t="inlineStr">
@@ -25763,7 +25763,7 @@
       </c>
       <c r="J487" t="inlineStr">
         <is>
-          <t>8 DE DICIEMBRE ZONA A COMITE MZA. C LOTE. 9 Arequipa-Arequipa-Tiabaya</t>
+          <t>PJ SANTA MARIA DE GUADALUPE MZA. E LOTE. 6 URB. STA MARIA DE GUADALUPE Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -25785,7 +25785,7 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>C001329398</t>
+          <t>C001212936</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
@@ -25795,12 +25795,12 @@
       </c>
       <c r="F488" s="2" t="inlineStr">
         <is>
-          <t>29508944</t>
+          <t>29504728</t>
         </is>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>DE LA CRUZ MAMANI GREGORIO</t>
+          <t>MAMANI HUISA MARINA JESUS</t>
         </is>
       </c>
       <c r="H488" t="inlineStr">
@@ -25815,7 +25815,7 @@
       </c>
       <c r="J488" t="inlineStr">
         <is>
-          <t>PJ 8 DE DICIEMBRE MZA. C LOTE. 11 URB. PJ 8 DE DICIEMBRE Arequipa-Arequipa-Tiabaya</t>
+          <t>STA MARIA DE GUADALUPE COMITE MZA. E LOTE. 1 URB. TIABAYA Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -25837,7 +25837,7 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>C001523060</t>
+          <t>C001668838</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
@@ -25847,12 +25847,12 @@
       </c>
       <c r="F489" s="2" t="inlineStr">
         <is>
-          <t>43353413</t>
+          <t>29508718</t>
         </is>
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>TTURO QUISPE ROXANA LIZI</t>
+          <t>CALSINA PAREDES ELSA NATIVIDAD</t>
         </is>
       </c>
       <c r="H489" t="inlineStr">
@@ -25867,7 +25867,7 @@
       </c>
       <c r="J489" t="inlineStr">
         <is>
-          <t>PJ SANTA MARIA DE GUADALUPE MZA. E LOTE. 6 URB. STA MARIA DE GUADALUPE Arequipa-Arequipa-Tiabaya</t>
+          <t>VILLA LOS ÁNGELES MZA. B LOTE. 7 URB. VILLA LOS ÁNGELES Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -25889,7 +25889,7 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>C001212936</t>
+          <t>C001615577</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
@@ -25899,12 +25899,12 @@
       </c>
       <c r="F490" s="2" t="inlineStr">
         <is>
-          <t>29504728</t>
+          <t>29739181</t>
         </is>
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>MAMANI HUISA MARINA JESUS</t>
+          <t>TTURO JERI NELLY SILVIA</t>
         </is>
       </c>
       <c r="H490" t="inlineStr">
@@ -25919,7 +25919,7 @@
       </c>
       <c r="J490" t="inlineStr">
         <is>
-          <t>STA MARIA DE GUADALUPE COMITE MZA. E LOTE. 1 URB. TIABAYA Arequipa-Arequipa-Tiabaya</t>
+          <t>PP JJ STA MARIA DE GUADALUPE MZA. D LOTE. 6 URB. STA MARIA DE GUADALUPE Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -25941,7 +25941,7 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>C001668838</t>
+          <t>C003001279</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
@@ -25951,12 +25951,12 @@
       </c>
       <c r="F491" s="2" t="inlineStr">
         <is>
-          <t>29508718</t>
+          <t>45781675</t>
         </is>
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>CALSINA PAREDES ELSA NATIVIDAD</t>
+          <t>MAQUERA CARI YUDY KEYLA</t>
         </is>
       </c>
       <c r="H491" t="inlineStr">
@@ -25971,7 +25971,7 @@
       </c>
       <c r="J491" t="inlineStr">
         <is>
-          <t>VILLA LOS ÁNGELES MZA. B LOTE. 7 URB. VILLA LOS ÁNGELES Arequipa-Arequipa-Tiabaya</t>
+          <t>santa María de Guadalupe zona b mz c comité 4 sub lote 1b</t>
         </is>
       </c>
     </row>
@@ -25993,7 +25993,7 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>C001615577</t>
+          <t>C001696909</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
@@ -26003,12 +26003,12 @@
       </c>
       <c r="F492" s="2" t="inlineStr">
         <is>
-          <t>29739181</t>
+          <t>40773847</t>
         </is>
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>TTURO JERI NELLY SILVIA</t>
+          <t>CHOQUELUQUE HUACANTARA PILAR ROXANA</t>
         </is>
       </c>
       <c r="H492" t="inlineStr">
@@ -26023,7 +26023,7 @@
       </c>
       <c r="J492" t="inlineStr">
         <is>
-          <t>PP JJ STA MARIA DE GUADALUPE MZA. D LOTE. 6 URB. STA MARIA DE GUADALUPE Arequipa-Arequipa-Tiabaya</t>
+          <t>P J SANTA MARIA DE GUADALUPE C LOTE. 4 URB. P J SANTA MARIA DE GUADALUPE Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -26045,7 +26045,7 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>C003001279</t>
+          <t>C003007005</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
@@ -26055,12 +26055,12 @@
       </c>
       <c r="F493" s="2" t="inlineStr">
         <is>
-          <t>45781675</t>
+          <t>30962755</t>
         </is>
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>MAQUERA CARI YUDY KEYLA</t>
+          <t>IQUIAPAZA FUENTES MARIA LUZ</t>
         </is>
       </c>
       <c r="H493" t="inlineStr">
@@ -26075,7 +26075,7 @@
       </c>
       <c r="J493" t="inlineStr">
         <is>
-          <t>santa María de Guadalupe zona b mz c comité 4 sub lote 1b</t>
+          <t>pueblo joven santa  María de Guadalupe  comité  2 mz.l lote 2</t>
         </is>
       </c>
     </row>
@@ -26097,7 +26097,7 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>C001696909</t>
+          <t>C003007006</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
@@ -26107,12 +26107,12 @@
       </c>
       <c r="F494" s="2" t="inlineStr">
         <is>
-          <t>40773847</t>
+          <t>72711863</t>
         </is>
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>CHOQUELUQUE HUACANTARA PILAR ROXANA</t>
+          <t>SIVINCHA QUISPE YAMYLE PAMELA</t>
         </is>
       </c>
       <c r="H494" t="inlineStr">
@@ -26127,7 +26127,7 @@
       </c>
       <c r="J494" t="inlineStr">
         <is>
-          <t>P J SANTA MARIA DE GUADALUPE C LOTE. 4 URB. P J SANTA MARIA DE GUADALUPE Arequipa-Arequipa-Tiabaya</t>
+          <t>santa  María de Guadalupe comité 1  mz e lote 5</t>
         </is>
       </c>
     </row>
@@ -26149,22 +26149,22 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>C003007005</t>
+          <t>C001649994</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F495" s="2" t="inlineStr">
         <is>
-          <t>30962755</t>
+          <t>10435782014</t>
         </is>
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>IQUIAPAZA FUENTES MARIA LUZ</t>
+          <t>MAMANI MAYTA MARIA ELENA</t>
         </is>
       </c>
       <c r="H495" t="inlineStr">
@@ -26179,7 +26179,7 @@
       </c>
       <c r="J495" t="inlineStr">
         <is>
-          <t>pueblo joven santa  María de Guadalupe  comité  2 mz.l lote 2</t>
+          <t>COMITE 3 MZA. G LOTE. 6 URB. SAN PEDRO TIABAYA Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -26201,22 +26201,22 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>C003007006</t>
+          <t>C001466615</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F496" s="2" t="inlineStr">
         <is>
-          <t>72711863</t>
+          <t>10293620453</t>
         </is>
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>SIVINCHA QUISPE YAMYLE PAMELA</t>
+          <t>AGUILAR QUISPE AGRIPINA</t>
         </is>
       </c>
       <c r="H496" t="inlineStr">
@@ -26231,7 +26231,7 @@
       </c>
       <c r="J496" t="inlineStr">
         <is>
-          <t>santa  María de Guadalupe comité 1  mz e lote 5</t>
+          <t>ZONA A  COMITE 3 MZA. H LOTE. 4 URB. PJ 8 DE DICIEMBRE Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -26253,22 +26253,22 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>C001649994</t>
+          <t>C001668837</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F497" s="2" t="inlineStr">
         <is>
-          <t>10435782014</t>
+          <t>42420761</t>
         </is>
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>MAMANI MAYTA MARIA ELENA</t>
+          <t>CANAZA ZAPATA DE LAYME LUZ MARINA</t>
         </is>
       </c>
       <c r="H497" t="inlineStr">
@@ -26283,7 +26283,7 @@
       </c>
       <c r="J497" t="inlineStr">
         <is>
-          <t>COMITE 3 MZA. G LOTE. 6 URB. SAN PEDRO TIABAYA Arequipa-Arequipa-Tiabaya</t>
+          <t>AV. URB LOS PERALES MZA. G LOTE. 2 URB. URB LOS PERALES Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -26305,22 +26305,22 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>C001466615</t>
+          <t>C004210158</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F498" s="2" t="inlineStr">
         <is>
-          <t>10293620453</t>
+          <t>29510715</t>
         </is>
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>AGUILAR QUISPE AGRIPINA</t>
+          <t>CALSINA PACCO ALICIA GRACIELA</t>
         </is>
       </c>
       <c r="H498" t="inlineStr">
@@ -26335,7 +26335,7 @@
       </c>
       <c r="J498" t="inlineStr">
         <is>
-          <t>ZONA A  COMITE 3 MZA. H LOTE. 4 URB. PJ 8 DE DICIEMBRE Arequipa-Arequipa-Tiabaya</t>
+          <t>Calle Prolongación Miguel Grau Y-3</t>
         </is>
       </c>
     </row>
@@ -26357,7 +26357,7 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>C001668837</t>
+          <t>C001483880</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
@@ -26367,12 +26367,12 @@
       </c>
       <c r="F499" s="2" t="inlineStr">
         <is>
-          <t>42420761</t>
+          <t>40599559</t>
         </is>
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>CANAZA ZAPATA DE LAYME LUZ MARINA</t>
+          <t>CHOQUEMAMANI ARENAS FLORA</t>
         </is>
       </c>
       <c r="H499" t="inlineStr">
@@ -26387,7 +26387,7 @@
       </c>
       <c r="J499" t="inlineStr">
         <is>
-          <t>AV. URB LOS PERALES MZA. G LOTE. 2 URB. URB LOS PERALES Arequipa-Arequipa-Tiabaya</t>
+          <t>MCDO. MERCADO TIABAYA URB. P T TIABAYA PSTO. 2 Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -26409,7 +26409,7 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>C004210158</t>
+          <t>C001505838</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
@@ -26419,12 +26419,12 @@
       </c>
       <c r="F500" s="2" t="inlineStr">
         <is>
-          <t>29510715</t>
+          <t>30963282</t>
         </is>
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>CALSINA PACCO ALICIA GRACIELA</t>
+          <t>TRAVERZO PALACIOS BELKYS ELINOL</t>
         </is>
       </c>
       <c r="H500" t="inlineStr">
@@ -26439,7 +26439,7 @@
       </c>
       <c r="J500" t="inlineStr">
         <is>
-          <t>Calle Prolongación Miguel Grau Y-3</t>
+          <t>CL. CALLE BOLIVAR NRO. 122 URB. TIABAYA Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -26461,7 +26461,7 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>C001483880</t>
+          <t>C004191120</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
@@ -26471,12 +26471,12 @@
       </c>
       <c r="F501" s="2" t="inlineStr">
         <is>
-          <t>40599559</t>
+          <t>71074498</t>
         </is>
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>CHOQUEMAMANI ARENAS FLORA</t>
+          <t>MAYTA CHIHUAYRO DE NINA SUSANA</t>
         </is>
       </c>
       <c r="H501" t="inlineStr">
@@ -26491,7 +26491,7 @@
       </c>
       <c r="J501" t="inlineStr">
         <is>
-          <t>MCDO. MERCADO TIABAYA URB. P T TIABAYA PSTO. 2 Arequipa-Arequipa-Tiabaya</t>
+          <t>mcdo San Martín de Porres puesto 1</t>
         </is>
       </c>
     </row>
@@ -26513,7 +26513,7 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>C001505838</t>
+          <t>C001200050</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
@@ -26523,12 +26523,12 @@
       </c>
       <c r="F502" s="2" t="inlineStr">
         <is>
-          <t>30963282</t>
+          <t>29479400</t>
         </is>
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>TRAVERZO PALACIOS BELKYS ELINOL</t>
+          <t>CHAVEZ DE VILLANUEVA ALBERTA CAYETANA</t>
         </is>
       </c>
       <c r="H502" t="inlineStr">
@@ -26543,7 +26543,7 @@
       </c>
       <c r="J502" t="inlineStr">
         <is>
-          <t>CL. CALLE BOLIVAR NRO. 122 URB. TIABAYA Arequipa-Arequipa-Tiabaya</t>
+          <t>AV. MERCADO TIABAYA URB. PT TIABAYA PSTO. 7 Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -26565,22 +26565,22 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>C004191120</t>
+          <t>C001212741</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F503" s="2" t="inlineStr">
         <is>
-          <t>71074498</t>
+          <t>10295094571</t>
         </is>
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>MAYTA CHIHUAYRO DE NINA SUSANA</t>
+          <t>HURTADO DE ALARCON ALICIA</t>
         </is>
       </c>
       <c r="H503" t="inlineStr">
@@ -26595,14 +26595,14 @@
       </c>
       <c r="J503" t="inlineStr">
         <is>
-          <t>mcdo San Martín de Porres puesto 1</t>
+          <t>CL. JUNIN NRO. 216 URB. PT TIABAYA Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>2026-09-16 00:00:00</t>
+          <t>2026-09-17 00:00:00</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -26617,22 +26617,22 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>C001200050</t>
+          <t>C004192633</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F504" s="2" t="inlineStr">
         <is>
-          <t>29479400</t>
+          <t>20614438020</t>
         </is>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>CHAVEZ DE VILLANUEVA ALBERTA CAYETANA</t>
+          <t>MUNDO EMPRESARIAL LDC S.A.C.</t>
         </is>
       </c>
       <c r="H504" t="inlineStr">
@@ -26647,14 +26647,14 @@
       </c>
       <c r="J504" t="inlineStr">
         <is>
-          <t>AV. MERCADO TIABAYA URB. PT TIABAYA PSTO. 7 Arequipa-Arequipa-Tiabaya</t>
+          <t>CAL. COLON NRO. 200</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>2026-09-16 00:00:00</t>
+          <t>2026-09-17 00:00:00</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -26669,22 +26669,22 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>C001212741</t>
+          <t>C001486690</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F505" s="2" t="inlineStr">
         <is>
-          <t>10295094571</t>
+          <t>44271776</t>
         </is>
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>HURTADO DE ALARCON ALICIA</t>
+          <t>DIAZ CASTILLO LILIBETH MILAGROS</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">
@@ -26699,7 +26699,7 @@
       </c>
       <c r="J505" t="inlineStr">
         <is>
-          <t>CL. JUNIN NRO. 216 URB. PT TIABAYA Arequipa-Arequipa-Tiabaya</t>
+          <t>CL. COLON NRO. 200 URB. PT TIABAYA Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -26721,22 +26721,22 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>C004192633</t>
+          <t>C001649715</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F506" s="2" t="inlineStr">
         <is>
-          <t>20614438020</t>
+          <t>29505199</t>
         </is>
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>MUNDO EMPRESARIAL LDC S.A.C.</t>
+          <t>ESCALANTE DURAND BERNARDINO EDWIN</t>
         </is>
       </c>
       <c r="H506" t="inlineStr">
@@ -26751,7 +26751,7 @@
       </c>
       <c r="J506" t="inlineStr">
         <is>
-          <t>CAL. COLON NRO. 200</t>
+          <t>CL. ARICA NRO. 108 URB. PT TIABAYA Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -26773,7 +26773,7 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>C001486690</t>
+          <t>C004153609</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
@@ -26783,12 +26783,12 @@
       </c>
       <c r="F507" s="2" t="inlineStr">
         <is>
-          <t>44271776</t>
+          <t>29507717</t>
         </is>
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>DIAZ CASTILLO LILIBETH MILAGROS</t>
+          <t>CASTILLO DE DIAZ JULIA</t>
         </is>
       </c>
       <c r="H507" t="inlineStr">
@@ -26803,7 +26803,7 @@
       </c>
       <c r="J507" t="inlineStr">
         <is>
-          <t>CL. COLON NRO. 200 URB. PT TIABAYA Arequipa-Arequipa-Tiabaya</t>
+          <t>Dirección  calle  colon 200 Tiabaya</t>
         </is>
       </c>
     </row>
@@ -26825,7 +26825,7 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>C001649715</t>
+          <t>C001208172</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
@@ -26835,12 +26835,12 @@
       </c>
       <c r="F508" s="2" t="inlineStr">
         <is>
-          <t>29505199</t>
+          <t>29512076</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>ESCALANTE DURAND BERNARDINO EDWIN</t>
+          <t>LOAYZA CALCINA MARIVEL MILVIA</t>
         </is>
       </c>
       <c r="H508" t="inlineStr">
@@ -26855,7 +26855,7 @@
       </c>
       <c r="J508" t="inlineStr">
         <is>
-          <t>CL. ARICA NRO. 108 URB. PT TIABAYA Arequipa-Arequipa-Tiabaya</t>
+          <t>AV. AV AREQUIPA NRO. 323 URB. PT TIABAYA Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -26877,7 +26877,7 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>C004153609</t>
+          <t>C004153613</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
@@ -26887,12 +26887,12 @@
       </c>
       <c r="F509" s="2" t="inlineStr">
         <is>
-          <t>29507717</t>
+          <t>62247798</t>
         </is>
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>CASTILLO DE DIAZ JULIA</t>
+          <t>CUNO LOAYZA MAURICIO HAROL</t>
         </is>
       </c>
       <c r="H509" t="inlineStr">
@@ -26907,7 +26907,7 @@
       </c>
       <c r="J509" t="inlineStr">
         <is>
-          <t>Dirección  calle  colon 200 Tiabaya</t>
+          <t>av  Arequipa  323 Tiabaya</t>
         </is>
       </c>
     </row>
@@ -26929,7 +26929,7 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>C001208172</t>
+          <t>C003001066</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
@@ -26939,12 +26939,12 @@
       </c>
       <c r="F510" s="2" t="inlineStr">
         <is>
-          <t>29512076</t>
+          <t>29506037</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>LOAYZA CALCINA MARIVEL MILVIA</t>
+          <t>CCAHUANA VIVANCO VICENTINA</t>
         </is>
       </c>
       <c r="H510" t="inlineStr">
@@ -26959,7 +26959,7 @@
       </c>
       <c r="J510" t="inlineStr">
         <is>
-          <t>AV. AV AREQUIPA NRO. 323 URB. PT TIABAYA Arequipa-Arequipa-Tiabaya</t>
+          <t>Mercado San Martín Puesto 08</t>
         </is>
       </c>
     </row>
@@ -26981,7 +26981,7 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>C004153613</t>
+          <t>C004215044</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
@@ -26991,12 +26991,12 @@
       </c>
       <c r="F511" s="2" t="inlineStr">
         <is>
-          <t>62247798</t>
+          <t>46863178</t>
         </is>
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>CUNO LOAYZA MAURICIO HAROL</t>
+          <t>OSORIO CCAHUANA PERCY RAUL</t>
         </is>
       </c>
       <c r="H511" t="inlineStr">
@@ -27011,7 +27011,7 @@
       </c>
       <c r="J511" t="inlineStr">
         <is>
-          <t>av  Arequipa  323 Tiabaya</t>
+          <t>Calle Bolivar 124</t>
         </is>
       </c>
     </row>
@@ -27033,7 +27033,7 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>C003001066</t>
+          <t>C004059983</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
@@ -27043,12 +27043,12 @@
       </c>
       <c r="F512" s="2" t="inlineStr">
         <is>
-          <t>29506037</t>
+          <t>29505152</t>
         </is>
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>CCAHUANA VIVANCO VICENTINA</t>
+          <t>LOBATON MACHACA OLINDA</t>
         </is>
       </c>
       <c r="H512" t="inlineStr">
@@ -27063,7 +27063,7 @@
       </c>
       <c r="J512" t="inlineStr">
         <is>
-          <t>Mercado San Martín Puesto 08</t>
+          <t>Calle bolivar 122 galería virgen de chapi interior puesto 6</t>
         </is>
       </c>
     </row>
@@ -27085,7 +27085,7 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>C004215044</t>
+          <t>C001695672</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
@@ -27095,12 +27095,12 @@
       </c>
       <c r="F513" s="2" t="inlineStr">
         <is>
-          <t>46863178</t>
+          <t>30463292</t>
         </is>
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>OSORIO CCAHUANA PERCY RAUL</t>
+          <t>QUISPE HUAMANTUMA MERY</t>
         </is>
       </c>
       <c r="H513" t="inlineStr">
@@ -27115,7 +27115,7 @@
       </c>
       <c r="J513" t="inlineStr">
         <is>
-          <t>Calle Bolivar 124</t>
+          <t>CL. BOLIVAR NRO. 115 URB. PT TIABAYA Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -27137,7 +27137,7 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>C004059983</t>
+          <t>C004208707</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
@@ -27147,12 +27147,12 @@
       </c>
       <c r="F514" s="2" t="inlineStr">
         <is>
-          <t>29505152</t>
+          <t>29509964</t>
         </is>
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>LOBATON MACHACA OLINDA</t>
+          <t>ORTIZ DIAZ NERY JOSEFA</t>
         </is>
       </c>
       <c r="H514" t="inlineStr">
@@ -27167,7 +27167,7 @@
       </c>
       <c r="J514" t="inlineStr">
         <is>
-          <t>Calle bolivar 122 galería virgen de chapi interior puesto 6</t>
+          <t>Calle Bolivar 113</t>
         </is>
       </c>
     </row>
@@ -27189,22 +27189,22 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>C001695672</t>
+          <t>C004192639</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F515" s="2" t="inlineStr">
         <is>
-          <t>30463292</t>
+          <t>10295119824</t>
         </is>
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>QUISPE HUAMANTUMA MERY</t>
+          <t>MACEDO MACHACA CARMEN ELIDA</t>
         </is>
       </c>
       <c r="H515" t="inlineStr">
@@ -27219,7 +27219,7 @@
       </c>
       <c r="J515" t="inlineStr">
         <is>
-          <t>CL. BOLIVAR NRO. 115 URB. PT TIABAYA Arequipa-Arequipa-Tiabaya</t>
+          <t>calle Bolívar 115 - tiabaya</t>
         </is>
       </c>
     </row>
@@ -27241,7 +27241,7 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>C004208707</t>
+          <t>C001380256</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
@@ -27251,12 +27251,12 @@
       </c>
       <c r="F516" s="2" t="inlineStr">
         <is>
-          <t>29509964</t>
+          <t>29633751</t>
         </is>
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>ORTIZ DIAZ NERY JOSEFA</t>
+          <t>LLACHO APAZA ANA MELBA</t>
         </is>
       </c>
       <c r="H516" t="inlineStr">
@@ -27271,7 +27271,7 @@
       </c>
       <c r="J516" t="inlineStr">
         <is>
-          <t>Calle Bolivar 113</t>
+          <t>MCDO. MERCADO TIABAYA URB. PT TIABAYA PSTO. 16 Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -27293,22 +27293,22 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>C004192639</t>
+          <t>C001329402</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F517" s="2" t="inlineStr">
         <is>
-          <t>10295119824</t>
+          <t>42250648</t>
         </is>
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>MACEDO MACHACA CARMEN ELIDA</t>
+          <t>MACEDO VILCAPAZA CHARO LUPE</t>
         </is>
       </c>
       <c r="H517" t="inlineStr">
@@ -27323,7 +27323,7 @@
       </c>
       <c r="J517" t="inlineStr">
         <is>
-          <t>calle Bolívar 115 - tiabaya</t>
+          <t>MCDO. MERCADO DE TIABAYA URB. PT TIABAYA PSTO. 12 Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -27345,7 +27345,7 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>C001380256</t>
+          <t>C001208623</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
@@ -27355,12 +27355,12 @@
       </c>
       <c r="F518" s="2" t="inlineStr">
         <is>
-          <t>29633751</t>
+          <t>29512305</t>
         </is>
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>LLACHO APAZA ANA MELBA</t>
+          <t>MAMANI MAYTA JULIA ALICIA</t>
         </is>
       </c>
       <c r="H518" t="inlineStr">
@@ -27375,7 +27375,7 @@
       </c>
       <c r="J518" t="inlineStr">
         <is>
-          <t>MCDO. MERCADO TIABAYA URB. PT TIABAYA PSTO. 16 Arequipa-Arequipa-Tiabaya</t>
+          <t>AV. MERCADO DE TIABAYA MZA. 10 URB. PT TIABAYA Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -27397,7 +27397,7 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>C001329402</t>
+          <t>C001501517</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
@@ -27407,12 +27407,12 @@
       </c>
       <c r="F519" s="2" t="inlineStr">
         <is>
-          <t>42250648</t>
+          <t>41512582</t>
         </is>
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>MACEDO VILCAPAZA CHARO LUPE</t>
+          <t>QUISPE HUAMANTUMA ALEJANDRINA</t>
         </is>
       </c>
       <c r="H519" t="inlineStr">
@@ -27427,7 +27427,7 @@
       </c>
       <c r="J519" t="inlineStr">
         <is>
-          <t>MCDO. MERCADO DE TIABAYA URB. PT TIABAYA PSTO. 12 Arequipa-Arequipa-Tiabaya</t>
+          <t>MCDO. MERCADO TIABAYA PSTO. 01 Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -27449,7 +27449,7 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>C001208623</t>
+          <t>C001210620</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
@@ -27459,12 +27459,12 @@
       </c>
       <c r="F520" s="2" t="inlineStr">
         <is>
-          <t>29512305</t>
+          <t>29476801</t>
         </is>
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>MAMANI MAYTA JULIA ALICIA</t>
+          <t>CALCINA DE PARIZACA VICENTINA INEZ</t>
         </is>
       </c>
       <c r="H520" t="inlineStr">
@@ -27479,7 +27479,7 @@
       </c>
       <c r="J520" t="inlineStr">
         <is>
-          <t>AV. MERCADO DE TIABAYA MZA. 10 URB. PT TIABAYA Arequipa-Arequipa-Tiabaya</t>
+          <t>AV. MERCADO DE TIABAYA URB. PT TIABAYA PSTO. 3 Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -27501,7 +27501,7 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>C001501517</t>
+          <t>C004198442</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
@@ -27511,12 +27511,12 @@
       </c>
       <c r="F521" s="2" t="inlineStr">
         <is>
-          <t>41512582</t>
+          <t>44069186</t>
         </is>
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>QUISPE HUAMANTUMA ALEJANDRINA</t>
+          <t>BEJAR ZAVALA FELICITAS</t>
         </is>
       </c>
       <c r="H521" t="inlineStr">
@@ -27531,7 +27531,7 @@
       </c>
       <c r="J521" t="inlineStr">
         <is>
-          <t>MCDO. MERCADO TIABAYA PSTO. 01 Arequipa-Arequipa-Tiabaya</t>
+          <t>Calle Canseco 107 Tiabaya</t>
         </is>
       </c>
     </row>
@@ -27553,7 +27553,7 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>C001210620</t>
+          <t>C001728782</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
@@ -27563,12 +27563,12 @@
       </c>
       <c r="F522" s="2" t="inlineStr">
         <is>
-          <t>29476801</t>
+          <t>29576850</t>
         </is>
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>CALCINA DE PARIZACA VICENTINA INEZ</t>
+          <t>YUCRA DE LIZARRAGA MARIA</t>
         </is>
       </c>
       <c r="H522" t="inlineStr">
@@ -27583,7 +27583,7 @@
       </c>
       <c r="J522" t="inlineStr">
         <is>
-          <t>AV. MERCADO DE TIABAYA URB. PT TIABAYA PSTO. 3 Arequipa-Arequipa-Tiabaya</t>
+          <t>MCDO. MERCADO TIABAYA URB. PT TIABAYA Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -27605,22 +27605,22 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>C004198442</t>
+          <t>C001686057</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F523" s="2" t="inlineStr">
         <is>
-          <t>44069186</t>
+          <t>10296558627</t>
         </is>
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>BEJAR ZAVALA FELICITAS</t>
+          <t>MANRIQUE CARDENAS ADALUZ TERESA</t>
         </is>
       </c>
       <c r="H523" t="inlineStr">
@@ -27635,7 +27635,7 @@
       </c>
       <c r="J523" t="inlineStr">
         <is>
-          <t>Calle Canseco 107 Tiabaya</t>
+          <t>CL. MILLER NRO. 213 URB. CP TIABAYA Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -27657,7 +27657,7 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>C001728782</t>
+          <t>C004213924</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
@@ -27667,12 +27667,12 @@
       </c>
       <c r="F524" s="2" t="inlineStr">
         <is>
-          <t>29576850</t>
+          <t>29510474</t>
         </is>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>YUCRA DE LIZARRAGA MARIA</t>
+          <t>NAJAR DE GALDOS KATYUZKA ELIZABETH</t>
         </is>
       </c>
       <c r="H524" t="inlineStr">
@@ -27687,7 +27687,7 @@
       </c>
       <c r="J524" t="inlineStr">
         <is>
-          <t>MCDO. MERCADO TIABAYA URB. PT TIABAYA Arequipa-Arequipa-Tiabaya</t>
+          <t>Cl. Bolognesi esquina calle pardo nro 406 urb.bolognesi</t>
         </is>
       </c>
     </row>
@@ -27709,7 +27709,7 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>C001686057</t>
+          <t>C001686080</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
@@ -27719,12 +27719,12 @@
       </c>
       <c r="F525" s="2" t="inlineStr">
         <is>
-          <t>10296558627</t>
+          <t>10405337148</t>
         </is>
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>MANRIQUE CARDENAS ADALUZ TERESA</t>
+          <t>GALVEZ PEÑA JESSICA MARIBEL</t>
         </is>
       </c>
       <c r="H525" t="inlineStr">
@@ -27739,7 +27739,7 @@
       </c>
       <c r="J525" t="inlineStr">
         <is>
-          <t>CL. MILLER NRO. 213 URB. CP TIABAYA Arequipa-Arequipa-Tiabaya</t>
+          <t>CL. BOLOGNESI NRO. 402 URB. P T TRADICIONAL Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -27761,22 +27761,22 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>C004213924</t>
+          <t>C001212838</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F526" s="2" t="inlineStr">
         <is>
-          <t>29510474</t>
+          <t>10295048820</t>
         </is>
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>NAJAR DE GALDOS KATYUZKA ELIZABETH</t>
+          <t>TELLES DE MOLINA GLORIA</t>
         </is>
       </c>
       <c r="H526" t="inlineStr">
@@ -27791,7 +27791,7 @@
       </c>
       <c r="J526" t="inlineStr">
         <is>
-          <t>Cl. Bolognesi esquina calle pardo nro 406 urb.bolognesi</t>
+          <t>CL. BOLOGNESI NRO. 318 Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -27813,22 +27813,22 @@
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>C001686080</t>
+          <t>C001732778</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F527" s="2" t="inlineStr">
         <is>
-          <t>10405337148</t>
+          <t>30963324</t>
         </is>
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>GALVEZ PEÑA JESSICA MARIBEL</t>
+          <t>TUPAYACHI RODRIGUEZ LUZ AMANDA</t>
         </is>
       </c>
       <c r="H527" t="inlineStr">
@@ -27843,14 +27843,14 @@
       </c>
       <c r="J527" t="inlineStr">
         <is>
-          <t>CL. BOLOGNESI NRO. 402 URB. P T TRADICIONAL Arequipa-Arequipa-Tiabaya</t>
+          <t>CL. PAZ SOLDÁN NRO. 119 URB. PT TIABAYA Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>2026-09-17 00:00:00</t>
+          <t>2026-09-18 00:00:00</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -27865,22 +27865,22 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>C001212838</t>
+          <t>C004210233</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F528" s="2" t="inlineStr">
         <is>
-          <t>10295048820</t>
+          <t>42362806</t>
         </is>
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>TELLES DE MOLINA GLORIA</t>
+          <t>ARCE USCA WILLY YURI</t>
         </is>
       </c>
       <c r="H528" t="inlineStr">
@@ -27895,14 +27895,14 @@
       </c>
       <c r="J528" t="inlineStr">
         <is>
-          <t>CL. BOLOGNESI NRO. 318 Arequipa-Arequipa-Tiabaya</t>
+          <t>José María arguedas mz g lote 3</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>2026-09-17 00:00:00</t>
+          <t>2026-09-18 00:00:00</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -27917,7 +27917,7 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>C001732778</t>
+          <t>C004215034</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
@@ -27927,12 +27927,12 @@
       </c>
       <c r="F529" s="2" t="inlineStr">
         <is>
-          <t>30963324</t>
+          <t>23995543</t>
         </is>
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>TUPAYACHI RODRIGUEZ LUZ AMANDA</t>
+          <t>MORON PAUCCARA HILDA</t>
         </is>
       </c>
       <c r="H529" t="inlineStr">
@@ -27947,7 +27947,7 @@
       </c>
       <c r="J529" t="inlineStr">
         <is>
-          <t>CL. PAZ SOLDÁN NRO. 119 URB. PT TIABAYA Arequipa-Arequipa-Tiabaya</t>
+          <t>Pueblo Joven José María arguedas mz l lote 10</t>
         </is>
       </c>
     </row>
@@ -27969,7 +27969,7 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>C004210233</t>
+          <t>C001572523</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
@@ -27979,12 +27979,12 @@
       </c>
       <c r="F530" s="2" t="inlineStr">
         <is>
-          <t>42362806</t>
+          <t>29258946</t>
         </is>
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>ARCE USCA WILLY YURI</t>
+          <t>OJEDA HERRERA IGNACIO EUSEBIO</t>
         </is>
       </c>
       <c r="H530" t="inlineStr">
@@ -27999,7 +27999,7 @@
       </c>
       <c r="J530" t="inlineStr">
         <is>
-          <t>José María arguedas mz g lote 3</t>
+          <t>CL. LOS JAZMINES MZA. C LOTE. 7 Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -28021,22 +28021,22 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>C004215034</t>
+          <t>C001492956</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F531" s="2" t="inlineStr">
         <is>
-          <t>23995543</t>
+          <t>10295103871</t>
         </is>
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>MORON PAUCCARA HILDA</t>
+          <t>PERALTA LUNA JACQUELINE NATALIA</t>
         </is>
       </c>
       <c r="H531" t="inlineStr">
@@ -28051,7 +28051,7 @@
       </c>
       <c r="J531" t="inlineStr">
         <is>
-          <t>Pueblo Joven José María arguedas mz l lote 10</t>
+          <t>CL. LOS JAZMINES ESQUINA CON NRO. 103 URB. SAN JOSE TIABAYA Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -28073,7 +28073,7 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>C001572523</t>
+          <t>C001212414</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
@@ -28083,12 +28083,12 @@
       </c>
       <c r="F532" s="2" t="inlineStr">
         <is>
-          <t>29258946</t>
+          <t>29506807</t>
         </is>
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>OJEDA HERRERA IGNACIO EUSEBIO</t>
+          <t>CCASANI JUARES CELIA</t>
         </is>
       </c>
       <c r="H532" t="inlineStr">
@@ -28103,7 +28103,7 @@
       </c>
       <c r="J532" t="inlineStr">
         <is>
-          <t>CL. LOS JAZMINES MZA. C LOTE. 7 Arequipa-Arequipa-Tiabaya</t>
+          <t>CL. LAS FLORES NRO. 109 URB. SAN JOSE TIABAYA Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -28125,7 +28125,7 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>C001492956</t>
+          <t>C001214771</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
@@ -28135,12 +28135,12 @@
       </c>
       <c r="F533" s="2" t="inlineStr">
         <is>
-          <t>10295103871</t>
+          <t>10295085865</t>
         </is>
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>PERALTA LUNA JACQUELINE NATALIA</t>
+          <t>VALDIVIA OJEDA LEONIDAS FRANCISCO</t>
         </is>
       </c>
       <c r="H533" t="inlineStr">
@@ -28155,7 +28155,7 @@
       </c>
       <c r="J533" t="inlineStr">
         <is>
-          <t>CL. LOS JAZMINES ESQUINA CON NRO. 103 URB. SAN JOSE TIABAYA Arequipa-Arequipa-Tiabaya</t>
+          <t>AV. ANDRES BELAUNDE NRO. 206 Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -28177,22 +28177,22 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>C001212414</t>
+          <t>C001461777</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F534" s="2" t="inlineStr">
         <is>
-          <t>29506807</t>
+          <t>10431094814</t>
         </is>
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>CCASANI JUARES CELIA</t>
+          <t>VILCA APAZA DEYSI JANETH</t>
         </is>
       </c>
       <c r="H534" t="inlineStr">
@@ -28207,7 +28207,7 @@
       </c>
       <c r="J534" t="inlineStr">
         <is>
-          <t>CL. LAS FLORES NRO. 109 URB. SAN JOSE TIABAYA Arequipa-Arequipa-Tiabaya</t>
+          <t>AV. VICTOR ANDRES BELAUNDE NRO. 502 URB. SAN JOSE DE TIABAYA Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -28229,7 +28229,7 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>C001214771</t>
+          <t>C004042230</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
@@ -28239,12 +28239,12 @@
       </c>
       <c r="F535" s="2" t="inlineStr">
         <is>
-          <t>10295085865</t>
+          <t>10439103685</t>
         </is>
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>VALDIVIA OJEDA LEONIDAS FRANCISCO</t>
+          <t>QUICCAÑO LEON HENRY SIMON</t>
         </is>
       </c>
       <c r="H535" t="inlineStr">
@@ -28259,7 +28259,7 @@
       </c>
       <c r="J535" t="inlineStr">
         <is>
-          <t>AV. ANDRES BELAUNDE NRO. 206 Arequipa-Arequipa-Tiabaya</t>
+          <t>Calle Tupac Amaru, 106 San José</t>
         </is>
       </c>
     </row>
@@ -28281,22 +28281,22 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>C001461777</t>
+          <t>C001214197</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F536" s="2" t="inlineStr">
         <is>
-          <t>10431094814</t>
+          <t>29512108</t>
         </is>
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>VILCA APAZA DEYSI JANETH</t>
+          <t>CALCINA JARA DE QUISPE LETHY ELENA</t>
         </is>
       </c>
       <c r="H536" t="inlineStr">
@@ -28311,7 +28311,7 @@
       </c>
       <c r="J536" t="inlineStr">
         <is>
-          <t>AV. VICTOR ANDRES BELAUNDE NRO. 502 URB. SAN JOSE DE TIABAYA Arequipa-Arequipa-Tiabaya</t>
+          <t>CL. LAS DELIAS NRO. 24 URB. PAMPAS NUEVAS TIABAYA Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -28333,22 +28333,22 @@
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>C004042230</t>
+          <t>C001390949</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F537" s="2" t="inlineStr">
         <is>
-          <t>10439103685</t>
+          <t>29507916</t>
         </is>
       </c>
       <c r="G537" t="inlineStr">
         <is>
-          <t>QUICCAÑO LEON HENRY SIMON</t>
+          <t>CARI SONCCO JESUSA ISIDORA</t>
         </is>
       </c>
       <c r="H537" t="inlineStr">
@@ -28363,7 +28363,7 @@
       </c>
       <c r="J537" t="inlineStr">
         <is>
-          <t>Calle Tupac Amaru, 106 San José</t>
+          <t>CL. MARIANO MELGAR COMITE 4 MZA. 4 LOTE. 4 URB. SAN JOSE TIABAYA Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -28385,7 +28385,7 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>C001214197</t>
+          <t>C001627452</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
@@ -28395,12 +28395,12 @@
       </c>
       <c r="F538" s="2" t="inlineStr">
         <is>
-          <t>29512108</t>
+          <t>41223577</t>
         </is>
       </c>
       <c r="G538" t="inlineStr">
         <is>
-          <t>CALCINA JARA DE QUISPE LETHY ELENA</t>
+          <t>VILCA PALLI NILO ALBERTO</t>
         </is>
       </c>
       <c r="H538" t="inlineStr">
@@ -28415,7 +28415,7 @@
       </c>
       <c r="J538" t="inlineStr">
         <is>
-          <t>CL. LAS DELIAS NRO. 24 URB. PAMPAS NUEVAS TIABAYA Arequipa-Arequipa-Tiabaya</t>
+          <t>MARIANO MELGAR MZA. F LOTE. 1 URB. TIABAYA Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -28437,7 +28437,7 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>C001390949</t>
+          <t>C001212413</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
@@ -28447,12 +28447,12 @@
       </c>
       <c r="F539" s="2" t="inlineStr">
         <is>
-          <t>29507916</t>
+          <t>29714064</t>
         </is>
       </c>
       <c r="G539" t="inlineStr">
         <is>
-          <t>CARI SONCCO JESUSA ISIDORA</t>
+          <t>CALCINA JARA MARILYN BIONI</t>
         </is>
       </c>
       <c r="H539" t="inlineStr">
@@ -28467,7 +28467,7 @@
       </c>
       <c r="J539" t="inlineStr">
         <is>
-          <t>CL. MARIANO MELGAR COMITE 4 MZA. 4 LOTE. 4 URB. SAN JOSE TIABAYA Arequipa-Arequipa-Tiabaya</t>
+          <t>CL. FRANCISCO MOSTAJO MZA. F LOTE. 6 URB. COMITE 4 TIABAYA Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -28489,7 +28489,7 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>C001627452</t>
+          <t>C001553942</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
@@ -28499,12 +28499,12 @@
       </c>
       <c r="F540" s="2" t="inlineStr">
         <is>
-          <t>41223577</t>
+          <t>29311833</t>
         </is>
       </c>
       <c r="G540" t="inlineStr">
         <is>
-          <t>VILCA PALLI NILO ALBERTO</t>
+          <t>SUCARI TUTACANO MARGARITA</t>
         </is>
       </c>
       <c r="H540" t="inlineStr">
@@ -28519,7 +28519,7 @@
       </c>
       <c r="J540" t="inlineStr">
         <is>
-          <t>MARIANO MELGAR MZA. F LOTE. 1 URB. TIABAYA Arequipa-Arequipa-Tiabaya</t>
+          <t>CL. JUAN MANUEL POLAR MZA. J LOTE. 11 Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -28541,7 +28541,7 @@
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>C001212413</t>
+          <t>C001458914</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
@@ -28551,12 +28551,12 @@
       </c>
       <c r="F541" s="2" t="inlineStr">
         <is>
-          <t>29714064</t>
+          <t>80624967</t>
         </is>
       </c>
       <c r="G541" t="inlineStr">
         <is>
-          <t>CALCINA JARA MARILYN BIONI</t>
+          <t>CHAMBI CCARI EDGAR</t>
         </is>
       </c>
       <c r="H541" t="inlineStr">
@@ -28571,7 +28571,7 @@
       </c>
       <c r="J541" t="inlineStr">
         <is>
-          <t>CL. FRANCISCO MOSTAJO MZA. F LOTE. 6 URB. COMITE 4 TIABAYA Arequipa-Arequipa-Tiabaya</t>
+          <t>CL. JUAN MANUEL POLAR NRO. 102 URB. SAN JOSE DE TIABAYA Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -28593,7 +28593,7 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>C001553942</t>
+          <t>C001630552</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
@@ -28603,12 +28603,12 @@
       </c>
       <c r="F542" s="2" t="inlineStr">
         <is>
-          <t>29311833</t>
+          <t>80386257</t>
         </is>
       </c>
       <c r="G542" t="inlineStr">
         <is>
-          <t>SUCARI TUTACANO MARGARITA</t>
+          <t>HANCCO SONCCO FILOMENA</t>
         </is>
       </c>
       <c r="H542" t="inlineStr">
@@ -28623,7 +28623,7 @@
       </c>
       <c r="J542" t="inlineStr">
         <is>
-          <t>CL. JUAN MANUEL POLAR MZA. J LOTE. 11 Arequipa-Arequipa-Tiabaya</t>
+          <t>VICTOR ANDRES BELAUNDE NRO. 305 URB. TIABAYA Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -28645,22 +28645,22 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>C001458914</t>
+          <t>C001210985</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F543" s="2" t="inlineStr">
         <is>
-          <t>80624967</t>
+          <t>10295116621</t>
         </is>
       </c>
       <c r="G543" t="inlineStr">
         <is>
-          <t>CHAMBI CCARI EDGAR</t>
+          <t>PANCCA LUQUE JUANA</t>
         </is>
       </c>
       <c r="H543" t="inlineStr">
@@ -28675,7 +28675,7 @@
       </c>
       <c r="J543" t="inlineStr">
         <is>
-          <t>CL. JUAN MANUEL POLAR NRO. 102 URB. SAN JOSE DE TIABAYA Arequipa-Arequipa-Tiabaya</t>
+          <t>AV. AVE VICTOR A BELAUNDE N-300-B NRO. 300-B MZA. MAZAA010 URB. SAN JOSE TIABAYA Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -28697,7 +28697,7 @@
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>C001630552</t>
+          <t>C004176557</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
@@ -28707,12 +28707,12 @@
       </c>
       <c r="F544" s="2" t="inlineStr">
         <is>
-          <t>80386257</t>
+          <t>40049269</t>
         </is>
       </c>
       <c r="G544" t="inlineStr">
         <is>
-          <t>HANCCO SONCCO FILOMENA</t>
+          <t>ZELA CHAMBILLA MARY VANESSA</t>
         </is>
       </c>
       <c r="H544" t="inlineStr">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="J544" t="inlineStr">
         <is>
-          <t>VICTOR ANDRES BELAUNDE NRO. 305 URB. TIABAYA Arequipa-Arequipa-Tiabaya</t>
+          <t>Tupac Amaru 104 San Jose</t>
         </is>
       </c>
     </row>
@@ -28749,22 +28749,22 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>C001210985</t>
+          <t>C004096793</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F545" s="2" t="inlineStr">
         <is>
-          <t>10295116621</t>
+          <t>29510944</t>
         </is>
       </c>
       <c r="G545" t="inlineStr">
         <is>
-          <t>PANCCA LUQUE JUANA</t>
+          <t>HUAYTA CALISAYA MATILDE</t>
         </is>
       </c>
       <c r="H545" t="inlineStr">
@@ -28779,7 +28779,7 @@
       </c>
       <c r="J545" t="inlineStr">
         <is>
-          <t>AV. AVE VICTOR A BELAUNDE N-300-B NRO. 300-B MZA. MAZAA010 URB. SAN JOSE TIABAYA Arequipa-Arequipa-Tiabaya</t>
+          <t>Av.  Tupac  Amaru 102 San José  Tiabaya</t>
         </is>
       </c>
     </row>
@@ -28801,7 +28801,7 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>C004176557</t>
+          <t>C001214480</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
@@ -28811,12 +28811,12 @@
       </c>
       <c r="F546" s="2" t="inlineStr">
         <is>
-          <t>40049269</t>
+          <t>41473770</t>
         </is>
       </c>
       <c r="G546" t="inlineStr">
         <is>
-          <t>ZELA CHAMBILLA MARY VANESSA</t>
+          <t>MUCHICA MAMANI MARIA LUZ</t>
         </is>
       </c>
       <c r="H546" t="inlineStr">
@@ -28831,7 +28831,7 @@
       </c>
       <c r="J546" t="inlineStr">
         <is>
-          <t>Tupac Amaru 104 San Jose</t>
+          <t>AV. VICTOR ANDRES BELAUNDE  COMIT MZA. M LOTE. 5 URB. SAN JOSE Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -28853,7 +28853,7 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>C004096793</t>
+          <t>C001212415</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
@@ -28863,12 +28863,12 @@
       </c>
       <c r="F547" s="2" t="inlineStr">
         <is>
-          <t>29510944</t>
+          <t>80077662</t>
         </is>
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>HUAYTA CALISAYA MATILDE</t>
+          <t>HUAMANI CASQUINA EPIFANIA</t>
         </is>
       </c>
       <c r="H547" t="inlineStr">
@@ -28883,7 +28883,7 @@
       </c>
       <c r="J547" t="inlineStr">
         <is>
-          <t>Av.  Tupac  Amaru 102 San José  Tiabaya</t>
+          <t>AV. ANDRES BELAUNDE NRO. 108 URB. ANDRES BELAUNDE TIABAYA Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -28905,7 +28905,7 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>C001214480</t>
+          <t>C001641427</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
@@ -28915,12 +28915,12 @@
       </c>
       <c r="F548" s="2" t="inlineStr">
         <is>
-          <t>41473770</t>
+          <t>80440313</t>
         </is>
       </c>
       <c r="G548" t="inlineStr">
         <is>
-          <t>MUCHICA MAMANI MARIA LUZ</t>
+          <t>OLANDA COAGUILA CLARA ENCARNACION</t>
         </is>
       </c>
       <c r="H548" t="inlineStr">
@@ -28935,7 +28935,7 @@
       </c>
       <c r="J548" t="inlineStr">
         <is>
-          <t>AV. VICTOR ANDRES BELAUNDE  COMIT MZA. M LOTE. 5 URB. SAN JOSE Arequipa-Arequipa-Tiabaya</t>
+          <t>AV. VICTOR ANDRES BELAUNDE S/N URB. TIABAYA Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -28957,7 +28957,7 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>C001212415</t>
+          <t>C004039878</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
@@ -28967,12 +28967,12 @@
       </c>
       <c r="F549" s="2" t="inlineStr">
         <is>
-          <t>80077662</t>
+          <t>29683016</t>
         </is>
       </c>
       <c r="G549" t="inlineStr">
         <is>
-          <t>HUAMANI CASQUINA EPIFANIA</t>
+          <t>PAREDES OLANDA MARCIA ISMENA</t>
         </is>
       </c>
       <c r="H549" t="inlineStr">
@@ -28987,7 +28987,7 @@
       </c>
       <c r="J549" t="inlineStr">
         <is>
-          <t>AV. ANDRES BELAUNDE NRO. 108 URB. ANDRES BELAUNDE TIABAYA Arequipa-Arequipa-Tiabaya</t>
+          <t>Av. Víctor Andrés Belaúnde s/n Pampas Nuevas</t>
         </is>
       </c>
     </row>
@@ -29009,7 +29009,7 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>C001641427</t>
+          <t>C001706882</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
@@ -29019,12 +29019,12 @@
       </c>
       <c r="F550" s="2" t="inlineStr">
         <is>
-          <t>80440313</t>
+          <t>1553286</t>
         </is>
       </c>
       <c r="G550" t="inlineStr">
         <is>
-          <t>OLANDA COAGUILA CLARA ENCARNACION</t>
+          <t>COTACALLAPA JOVE ANA NATTY</t>
         </is>
       </c>
       <c r="H550" t="inlineStr">
@@ -29039,7 +29039,7 @@
       </c>
       <c r="J550" t="inlineStr">
         <is>
-          <t>AV. VICTOR ANDRES BELAUNDE S/N URB. TIABAYA Arequipa-Arequipa-Tiabaya</t>
+          <t>CL. MADRID AMPLIACIÓN MICAELA BAST MZA. A LOTE. 6 URB. PAMPAS NUEVAS Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
@@ -29061,22 +29061,22 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>C004039878</t>
+          <t>C001201166</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F551" s="2" t="inlineStr">
         <is>
-          <t>29683016</t>
+          <t>10295063403</t>
         </is>
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>PAREDES OLANDA MARCIA ISMENA</t>
+          <t>HUANCA DE CALCINA EUSEBIA</t>
         </is>
       </c>
       <c r="H551" t="inlineStr">
@@ -29091,14 +29091,14 @@
       </c>
       <c r="J551" t="inlineStr">
         <is>
-          <t>Av. Víctor Andrés Belaúnde s/n Pampas Nuevas</t>
+          <t>CL. FRANCISCO BOLOGNESI NRO. C INT. 11 URB. CP MICAELA BASTIDAS Arequipa-Arequipa-Tiabaya</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>2026-09-18 00:00:00</t>
+          <t>2026-09-19 00:00:00</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -29113,7 +29113,7 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>C001706882</t>
+          <t>C001733041</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
@@ -29123,12 +29123,12 @@
       </c>
       <c r="F552" s="2" t="inlineStr">
         <is>
-          <t>1553286</t>
+          <t>40092048</t>
         </is>
       </c>
       <c r="G552" t="inlineStr">
         <is>
-          <t>COTACALLAPA JOVE ANA NATTY</t>
+          <t>PINTO MOLINA ROCIO DULCINEA</t>
         </is>
       </c>
       <c r="H552" t="inlineStr">
@@ -29138,19 +29138,19 @@
       </c>
       <c r="I552" t="inlineStr">
         <is>
-          <t>Tiabaya (Arequipa)</t>
+          <t>Socabaya (Arequipa)</t>
         </is>
       </c>
       <c r="J552" t="inlineStr">
         <is>
-          <t>CL. MADRID AMPLIACIÓN MICAELA BAST MZA. A LOTE. 6 URB. PAMPAS NUEVAS Arequipa-Arequipa-Tiabaya</t>
+          <t>AV. LAS PEÑAS NRO. 1006 MZA. B URB. BELLAPAMPA Arequipa-Arequipa-Socabaya</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>2026-09-18 00:00:00</t>
+          <t>2026-09-19 00:00:00</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -29165,22 +29165,22 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>C001201166</t>
+          <t>C001087436</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F553" s="2" t="inlineStr">
         <is>
-          <t>10295063403</t>
+          <t>41253260</t>
         </is>
       </c>
       <c r="G553" t="inlineStr">
         <is>
-          <t>HUANCA DE CALCINA EUSEBIA</t>
+          <t>VARGAS MOLINA MARILYN GIULIANA</t>
         </is>
       </c>
       <c r="H553" t="inlineStr">
@@ -29190,12 +29190,12 @@
       </c>
       <c r="I553" t="inlineStr">
         <is>
-          <t>Tiabaya (Arequipa)</t>
+          <t>Socabaya (Arequipa)</t>
         </is>
       </c>
       <c r="J553" t="inlineStr">
         <is>
-          <t>CL. FRANCISCO BOLOGNESI NRO. C INT. 11 URB. CP MICAELA BASTIDAS Arequipa-Arequipa-Tiabaya</t>
+          <t>CL. TUPAC AMARU NRO. 303 URB. BELLAPAMPA Arequipa-Arequipa-Socabaya</t>
         </is>
       </c>
     </row>
@@ -29217,7 +29217,7 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>C001733041</t>
+          <t>C001564504</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
@@ -29227,12 +29227,12 @@
       </c>
       <c r="F554" s="2" t="inlineStr">
         <is>
-          <t>40092048</t>
+          <t>8530520</t>
         </is>
       </c>
       <c r="G554" t="inlineStr">
         <is>
-          <t>PINTO MOLINA ROCIO DULCINEA</t>
+          <t>ARCE LAZO VICTORIA</t>
         </is>
       </c>
       <c r="H554" t="inlineStr">
@@ -29247,7 +29247,7 @@
       </c>
       <c r="J554" t="inlineStr">
         <is>
-          <t>AV. LAS PEÑAS NRO. 1006 MZA. B URB. BELLAPAMPA Arequipa-Arequipa-Socabaya</t>
+          <t>CL. NICOLAS DE PIEROLA NRO. 309 Arequipa-Arequipa-Socabaya</t>
         </is>
       </c>
     </row>
@@ -29269,22 +29269,22 @@
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>C001087436</t>
+          <t>C001115056</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F555" s="2" t="inlineStr">
         <is>
-          <t>41253260</t>
+          <t>10295018041</t>
         </is>
       </c>
       <c r="G555" t="inlineStr">
         <is>
-          <t>VARGAS MOLINA MARILYN GIULIANA</t>
+          <t>MARIN DE HUARANGA MARIA</t>
         </is>
       </c>
       <c r="H555" t="inlineStr">
@@ -29299,7 +29299,7 @@
       </c>
       <c r="J555" t="inlineStr">
         <is>
-          <t>CL. TUPAC AMARU NRO. 303 URB. BELLAPAMPA Arequipa-Arequipa-Socabaya</t>
+          <t>PJE. RICARDO PALMA INT. 4 URB. MCDO CIUDAD MI TRABAJO Arequipa-Arequipa-Socabaya</t>
         </is>
       </c>
     </row>
@@ -29321,7 +29321,7 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>C001564504</t>
+          <t>C001642913</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
@@ -29331,12 +29331,12 @@
       </c>
       <c r="F556" s="2" t="inlineStr">
         <is>
-          <t>8530520</t>
+          <t>2419360</t>
         </is>
       </c>
       <c r="G556" t="inlineStr">
         <is>
-          <t>ARCE LAZO VICTORIA</t>
+          <t>BEJAR MOLINA MARIELA</t>
         </is>
       </c>
       <c r="H556" t="inlineStr">
@@ -29351,7 +29351,7 @@
       </c>
       <c r="J556" t="inlineStr">
         <is>
-          <t>CL. NICOLAS DE PIEROLA NRO. 309 Arequipa-Arequipa-Socabaya</t>
+          <t>CL. RIMAC NRO. 104 URB. CIUDAD MI TRABAJO Arequipa-Arequipa-Socabaya</t>
         </is>
       </c>
     </row>
@@ -29373,22 +29373,22 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>C001115056</t>
+          <t>C004054461</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F557" s="2" t="inlineStr">
         <is>
-          <t>10295018041</t>
+          <t>29580105</t>
         </is>
       </c>
       <c r="G557" t="inlineStr">
         <is>
-          <t>MARIN DE HUARANGA MARIA</t>
+          <t>CAMPANO FRISANCHO ZOILA AURISTELA</t>
         </is>
       </c>
       <c r="H557" t="inlineStr">
@@ -29403,7 +29403,7 @@
       </c>
       <c r="J557" t="inlineStr">
         <is>
-          <t>PJE. RICARDO PALMA INT. 4 URB. MCDO CIUDAD MI TRABAJO Arequipa-Arequipa-Socabaya</t>
+          <t>Psje Gonzáles Prada/Esquina  Los  Rosales  # 100 C. Mi Trabajo</t>
         </is>
       </c>
     </row>
@@ -29425,7 +29425,7 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>C001642913</t>
+          <t>C004208802</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
@@ -29435,12 +29435,12 @@
       </c>
       <c r="F558" s="2" t="inlineStr">
         <is>
-          <t>2419360</t>
+          <t>5413715</t>
         </is>
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t>BEJAR MOLINA MARIELA</t>
+          <t>DIAZ CARO DANIA</t>
         </is>
       </c>
       <c r="H558" t="inlineStr">
@@ -29455,7 +29455,7 @@
       </c>
       <c r="J558" t="inlineStr">
         <is>
-          <t>CL. RIMAC NRO. 104 URB. CIUDAD MI TRABAJO Arequipa-Arequipa-Socabaya</t>
+          <t>Av independencia 402 ciudad mi trabajo, Socabaya</t>
         </is>
       </c>
     </row>
@@ -29477,7 +29477,7 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>C004054461</t>
+          <t>C001035887</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
@@ -29487,12 +29487,12 @@
       </c>
       <c r="F559" s="2" t="inlineStr">
         <is>
-          <t>29580105</t>
+          <t>4646206</t>
         </is>
       </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t>CAMPANO FRISANCHO ZOILA AURISTELA</t>
+          <t>PALOMINO BUSTINZA NILDA ELVIRA</t>
         </is>
       </c>
       <c r="H559" t="inlineStr">
@@ -29507,7 +29507,7 @@
       </c>
       <c r="J559" t="inlineStr">
         <is>
-          <t>Psje Gonzáles Prada/Esquina  Los  Rosales  # 100 C. Mi Trabajo</t>
+          <t>URB LARA MZA. B LOTE. 7 Arequipa-Arequipa-Socabaya</t>
         </is>
       </c>
     </row>
@@ -29529,7 +29529,7 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>C004208802</t>
+          <t>C001503451</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
@@ -29539,12 +29539,12 @@
       </c>
       <c r="F560" s="2" t="inlineStr">
         <is>
-          <t>5413715</t>
+          <t>29713527</t>
         </is>
       </c>
       <c r="G560" t="inlineStr">
         <is>
-          <t>DIAZ CARO DANIA</t>
+          <t>HUAICHO QUISPE YUDY AIDEE</t>
         </is>
       </c>
       <c r="H560" t="inlineStr">
@@ -29559,7 +29559,7 @@
       </c>
       <c r="J560" t="inlineStr">
         <is>
-          <t>Av independencia 402 ciudad mi trabajo, Socabaya</t>
+          <t>CL. MARIANO MELGAR NRO. 206 URB. 4 D EOCTUBRE Arequipa-Arequipa-Socabaya</t>
         </is>
       </c>
     </row>
@@ -29581,7 +29581,7 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>C001035887</t>
+          <t>C001694499</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
@@ -29591,12 +29591,12 @@
       </c>
       <c r="F561" s="2" t="inlineStr">
         <is>
-          <t>4646206</t>
+          <t>29654126</t>
         </is>
       </c>
       <c r="G561" t="inlineStr">
         <is>
-          <t>PALOMINO BUSTINZA NILDA ELVIRA</t>
+          <t>SUCA CHEJE OLIVIA ELIZABETH</t>
         </is>
       </c>
       <c r="H561" t="inlineStr">
@@ -29611,7 +29611,7 @@
       </c>
       <c r="J561" t="inlineStr">
         <is>
-          <t>URB LARA MZA. B LOTE. 7 Arequipa-Arequipa-Socabaya</t>
+          <t>CL. JORGE BASADRE NRO. 212 Arequipa-Arequipa-Socabaya</t>
         </is>
       </c>
     </row>
@@ -29633,7 +29633,7 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>C001503451</t>
+          <t>C004161282</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
@@ -29643,12 +29643,12 @@
       </c>
       <c r="F562" s="2" t="inlineStr">
         <is>
-          <t>29713527</t>
+          <t>40742482</t>
         </is>
       </c>
       <c r="G562" t="inlineStr">
         <is>
-          <t>HUAICHO QUISPE YUDY AIDEE</t>
+          <t>BAUTISTA LOPE ALFONSO</t>
         </is>
       </c>
       <c r="H562" t="inlineStr">
@@ -29663,7 +29663,7 @@
       </c>
       <c r="J562" t="inlineStr">
         <is>
-          <t>CL. MARIANO MELGAR NRO. 206 URB. 4 D EOCTUBRE Arequipa-Arequipa-Socabaya</t>
+          <t>Av. José Carlos   Mariátegui   318 4 de  octubre -socabaya</t>
         </is>
       </c>
     </row>
@@ -29685,7 +29685,7 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>C001694499</t>
+          <t>C001620548</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
@@ -29695,12 +29695,12 @@
       </c>
       <c r="F563" s="2" t="inlineStr">
         <is>
-          <t>29654126</t>
+          <t>27371334</t>
         </is>
       </c>
       <c r="G563" t="inlineStr">
         <is>
-          <t>SUCA CHEJE OLIVIA ELIZABETH</t>
+          <t>CIEZA COLUNCHE EUFEMIA</t>
         </is>
       </c>
       <c r="H563" t="inlineStr">
@@ -29715,7 +29715,7 @@
       </c>
       <c r="J563" t="inlineStr">
         <is>
-          <t>CL. JORGE BASADRE NRO. 212 Arequipa-Arequipa-Socabaya</t>
+          <t>AV. JOSE CARLOS MARIATEGUI NRO. 414 URB. 4 DE OCTUBRE Arequipa-Arequipa-Socabaya</t>
         </is>
       </c>
     </row>
@@ -29737,7 +29737,7 @@
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>C004161282</t>
+          <t>C004169939</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
@@ -29747,12 +29747,12 @@
       </c>
       <c r="F564" s="2" t="inlineStr">
         <is>
-          <t>40742482</t>
+          <t>29269712</t>
         </is>
       </c>
       <c r="G564" t="inlineStr">
         <is>
-          <t>BAUTISTA LOPE ALFONSO</t>
+          <t>LAZARO PUMA FELIPA DIONICIA</t>
         </is>
       </c>
       <c r="H564" t="inlineStr">
@@ -29767,7 +29767,7 @@
       </c>
       <c r="J564" t="inlineStr">
         <is>
-          <t>Av. José Carlos   Mariátegui   318 4 de  octubre -socabaya</t>
+          <t>manuel escorza N 8 - socabaya</t>
         </is>
       </c>
     </row>
@@ -29789,7 +29789,7 @@
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>C001620548</t>
+          <t>C001034522</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
@@ -29799,12 +29799,12 @@
       </c>
       <c r="F565" s="2" t="inlineStr">
         <is>
-          <t>27371334</t>
+          <t>42157733</t>
         </is>
       </c>
       <c r="G565" t="inlineStr">
         <is>
-          <t>CIEZA COLUNCHE EUFEMIA</t>
+          <t>GONZALES MELGAREJO VICTOR RICARDO</t>
         </is>
       </c>
       <c r="H565" t="inlineStr">
@@ -29819,7 +29819,7 @@
       </c>
       <c r="J565" t="inlineStr">
         <is>
-          <t>AV. JOSE CARLOS MARIATEGUI NRO. 414 URB. 4 DE OCTUBRE Arequipa-Arequipa-Socabaya</t>
+          <t>JR. CAL FERREÑAFE N200 NRO. 200 MZA. MAZAA090 URB. SAN MARTIN DE SOCABAYA Arequipa-Arequipa-Socabaya</t>
         </is>
       </c>
     </row>
@@ -29841,7 +29841,7 @@
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>C004169939</t>
+          <t>C001531667</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
@@ -29851,12 +29851,12 @@
       </c>
       <c r="F566" s="2" t="inlineStr">
         <is>
-          <t>29269712</t>
+          <t>30961798</t>
         </is>
       </c>
       <c r="G566" t="inlineStr">
         <is>
-          <t>LAZARO PUMA FELIPA DIONICIA</t>
+          <t>CAMA LEON GLORIA YANET</t>
         </is>
       </c>
       <c r="H566" t="inlineStr">
@@ -29871,7 +29871,7 @@
       </c>
       <c r="J566" t="inlineStr">
         <is>
-          <t>manuel escorza N 8 - socabaya</t>
+          <t>PJE. PASAJE NRO. 5 URB. SAN MARTIN DE SOCABAYA Arequipa-Arequipa-Socabaya</t>
         </is>
       </c>
     </row>
@@ -29893,7 +29893,7 @@
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>C001034522</t>
+          <t>C001490702</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
@@ -29903,12 +29903,12 @@
       </c>
       <c r="F567" s="2" t="inlineStr">
         <is>
-          <t>42157733</t>
+          <t>2297513</t>
         </is>
       </c>
       <c r="G567" t="inlineStr">
         <is>
-          <t>GONZALES MELGAREJO VICTOR RICARDO</t>
+          <t>MAMANI CCAMA MARIA ISABEL</t>
         </is>
       </c>
       <c r="H567" t="inlineStr">
@@ -29923,7 +29923,7 @@
       </c>
       <c r="J567" t="inlineStr">
         <is>
-          <t>JR. CAL FERREÑAFE N200 NRO. 200 MZA. MAZAA090 URB. SAN MARTIN DE SOCABAYA Arequipa-Arequipa-Socabaya</t>
+          <t>CL. TARATA NRO. 105 URB. SAN MARTIN DE SOCABAYA Arequipa-Arequipa-Socabaya</t>
         </is>
       </c>
     </row>
@@ -29945,22 +29945,22 @@
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>C001531667</t>
+          <t>C001039061</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F568" s="2" t="inlineStr">
         <is>
-          <t>30961798</t>
+          <t>10403965559</t>
         </is>
       </c>
       <c r="G568" t="inlineStr">
         <is>
-          <t>CAMA LEON GLORIA YANET</t>
+          <t>CONTRERAS ANDIA SANDRA</t>
         </is>
       </c>
       <c r="H568" t="inlineStr">
@@ -29975,7 +29975,7 @@
       </c>
       <c r="J568" t="inlineStr">
         <is>
-          <t>PJE. PASAJE NRO. 5 URB. SAN MARTIN DE SOCABAYA Arequipa-Arequipa-Socabaya</t>
+          <t>JR. CAL CHACHAPOYAS N502 NRO. 502 MZA. MAZAA120 URB. SAN MARTIN DE SOC Arequipa-Arequipa-Socabaya</t>
         </is>
       </c>
     </row>
@@ -29997,7 +29997,7 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>C001490702</t>
+          <t>C004008001</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
@@ -30007,12 +30007,12 @@
       </c>
       <c r="F569" s="2" t="inlineStr">
         <is>
-          <t>2297513</t>
+          <t>29588366</t>
         </is>
       </c>
       <c r="G569" t="inlineStr">
         <is>
-          <t>MAMANI CCAMA MARIA ISABEL</t>
+          <t>RAMIREZ TUDELA MARIO JOSE LUIS</t>
         </is>
       </c>
       <c r="H569" t="inlineStr">
@@ -30027,7 +30027,7 @@
       </c>
       <c r="J569" t="inlineStr">
         <is>
-          <t>CL. TARATA NRO. 105 URB. SAN MARTIN DE SOCABAYA Arequipa-Arequipa-Socabaya</t>
+          <t>Calle Chachapoyas 502 San Martin de Socabaya</t>
         </is>
       </c>
     </row>
@@ -30049,22 +30049,22 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>C001039061</t>
+          <t>C001684924</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F570" s="2" t="inlineStr">
         <is>
-          <t>10403965559</t>
+          <t>74235276</t>
         </is>
       </c>
       <c r="G570" t="inlineStr">
         <is>
-          <t>CONTRERAS ANDIA SANDRA</t>
+          <t>VIZA ROQUE LUZ MARINA</t>
         </is>
       </c>
       <c r="H570" t="inlineStr">
@@ -30079,7 +30079,7 @@
       </c>
       <c r="J570" t="inlineStr">
         <is>
-          <t>JR. CAL CHACHAPOYAS N502 NRO. 502 MZA. MAZAA120 URB. SAN MARTIN DE SOC Arequipa-Arequipa-Socabaya</t>
+          <t>CL. CHACHAPOYAS NRO. 517 URB. SAN MARTIN DE SOCABAYA Arequipa-Arequipa-Socabaya</t>
         </is>
       </c>
     </row>
@@ -30101,7 +30101,7 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>C004008001</t>
+          <t>C004207883</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
@@ -30111,12 +30111,12 @@
       </c>
       <c r="F571" s="2" t="inlineStr">
         <is>
-          <t>29588366</t>
+          <t>74204820</t>
         </is>
       </c>
       <c r="G571" t="inlineStr">
         <is>
-          <t>RAMIREZ TUDELA MARIO JOSE LUIS</t>
+          <t>AEDO MACHACA ADRIANA VALERY</t>
         </is>
       </c>
       <c r="H571" t="inlineStr">
@@ -30131,7 +30131,7 @@
       </c>
       <c r="J571" t="inlineStr">
         <is>
-          <t>Calle Chachapoyas 502 San Martin de Socabaya</t>
+          <t>Calle manzanitas 200</t>
         </is>
       </c>
     </row>
@@ -30153,22 +30153,22 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>C001684924</t>
+          <t>C004238534</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F572" s="2" t="inlineStr">
         <is>
-          <t>74235276</t>
+          <t>20497841632</t>
         </is>
       </c>
       <c r="G572" t="inlineStr">
         <is>
-          <t>VIZA ROQUE LUZ MARINA</t>
+          <t>COMERCIAL Y SERVICIOS ENJU'S E.I.R.L.</t>
         </is>
       </c>
       <c r="H572" t="inlineStr">
@@ -30183,7 +30183,7 @@
       </c>
       <c r="J572" t="inlineStr">
         <is>
-          <t>CL. CHACHAPOYAS NRO. 517 URB. SAN MARTIN DE SOCABAYA Arequipa-Arequipa-Socabaya</t>
+          <t>PJ. MANRIQUE NRO. 104</t>
         </is>
       </c>
     </row>
@@ -30205,22 +30205,22 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>C004207883</t>
+          <t>C001564389</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F573" s="2" t="inlineStr">
         <is>
-          <t>74204820</t>
+          <t>10714039925</t>
         </is>
       </c>
       <c r="G573" t="inlineStr">
         <is>
-          <t>AEDO MACHACA ADRIANA VALERY</t>
+          <t>SUNI PILCOMAMANI KARLA GABRIELA</t>
         </is>
       </c>
       <c r="H573" t="inlineStr">
@@ -30235,7 +30235,7 @@
       </c>
       <c r="J573" t="inlineStr">
         <is>
-          <t>Calle manzanitas 200</t>
+          <t>PJE. MANRIQUE NRO. 104 URB. LARA Arequipa-Arequipa-Socabaya</t>
         </is>
       </c>
     </row>
@@ -30257,22 +30257,22 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>C004238534</t>
+          <t>C004023446</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F574" s="2" t="inlineStr">
         <is>
-          <t>20497841632</t>
+          <t>41669914</t>
         </is>
       </c>
       <c r="G574" t="inlineStr">
         <is>
-          <t>COMERCIAL Y SERVICIOS ENJU'S E.I.R.L.</t>
+          <t>GOMEZ ARIAS CYNTHIA VANESSA</t>
         </is>
       </c>
       <c r="H574" t="inlineStr">
@@ -30287,7 +30287,7 @@
       </c>
       <c r="J574" t="inlineStr">
         <is>
-          <t>PJ. MANRIQUE NRO. 104</t>
+          <t>AV SALAVERRY 402 URB LARA</t>
         </is>
       </c>
     </row>
@@ -30309,7 +30309,7 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>C001564389</t>
+          <t>C001037724</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
@@ -30319,12 +30319,12 @@
       </c>
       <c r="F575" s="2" t="inlineStr">
         <is>
-          <t>10714039925</t>
+          <t>10295030092</t>
         </is>
       </c>
       <c r="G575" t="inlineStr">
         <is>
-          <t>SUNI PILCOMAMANI KARLA GABRIELA</t>
+          <t>OCHOCHOQUE MENDOZA CRISTINA</t>
         </is>
       </c>
       <c r="H575" t="inlineStr">
@@ -30339,116 +30339,12 @@
       </c>
       <c r="J575" t="inlineStr">
         <is>
-          <t>PJE. MANRIQUE NRO. 104 URB. LARA Arequipa-Arequipa-Socabaya</t>
-        </is>
-      </c>
-    </row>
-    <row r="576">
-      <c r="A576" t="inlineStr">
-        <is>
-          <t>2026-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="B576" t="inlineStr">
-        <is>
-          <t>RONALD LLULIAN SANDOVAL GANOZA</t>
-        </is>
-      </c>
-      <c r="C576" t="inlineStr">
-        <is>
-          <t>ROSET DISTRIBUCIONES EIRL</t>
-        </is>
-      </c>
-      <c r="D576" t="inlineStr">
-        <is>
-          <t>C004023446</t>
-        </is>
-      </c>
-      <c r="E576" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
-      <c r="F576" s="2" t="inlineStr">
-        <is>
-          <t>41669914</t>
-        </is>
-      </c>
-      <c r="G576" t="inlineStr">
-        <is>
-          <t>GOMEZ ARIAS CYNTHIA VANESSA</t>
-        </is>
-      </c>
-      <c r="H576" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="I576" t="inlineStr">
-        <is>
-          <t>Socabaya (Arequipa)</t>
-        </is>
-      </c>
-      <c r="J576" t="inlineStr">
-        <is>
-          <t>AV SALAVERRY 402 URB LARA</t>
-        </is>
-      </c>
-    </row>
-    <row r="577">
-      <c r="A577" t="inlineStr">
-        <is>
-          <t>2026-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="B577" t="inlineStr">
-        <is>
-          <t>RONALD LLULIAN SANDOVAL GANOZA</t>
-        </is>
-      </c>
-      <c r="C577" t="inlineStr">
-        <is>
-          <t>ROSET DISTRIBUCIONES EIRL</t>
-        </is>
-      </c>
-      <c r="D577" t="inlineStr">
-        <is>
-          <t>C001037724</t>
-        </is>
-      </c>
-      <c r="E577" t="inlineStr">
-        <is>
-          <t>RUC</t>
-        </is>
-      </c>
-      <c r="F577" s="2" t="inlineStr">
-        <is>
-          <t>10295030092</t>
-        </is>
-      </c>
-      <c r="G577" t="inlineStr">
-        <is>
-          <t>OCHOCHOQUE MENDOZA CRISTINA</t>
-        </is>
-      </c>
-      <c r="H577" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="I577" t="inlineStr">
-        <is>
-          <t>Socabaya (Arequipa)</t>
-        </is>
-      </c>
-      <c r="J577" t="inlineStr">
-        <is>
           <t>JR. CAL JOSE CARLOS MARIATEGUI N1 NRO. 104 MZA. MAZAA450 URB. 04 DE OCTUBRE Arequipa-Arequipa-Socabaya</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J577"/>
+  <autoFilter ref="A1:J575"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>